--- a/reports/member_funnel/downloads/member_funnel_1m_non_buyer.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1m_non_buyer.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E330"/>
+  <dimension ref="A1:E263"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -527,179 +527,179 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>hennessy</t>
+          <t>kk_4993751323</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>01030027773</t>
+          <t>01053138487</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>13296</t>
+          <t>309590</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>방문_하이브리드 오디언스</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>kk_4993751323</t>
+          <t>kk_3494319831</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>01053138487</t>
+          <t>01088337167</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>309590</t>
+          <t>245102</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>방문_하이브리드 오디언스</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>kk_3494319831</t>
+          <t>kk_4403816883</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>01088337167</t>
+          <t>01097910906</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>245102</t>
+          <t>280909</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>kk_4403816883</t>
+          <t>kk_4929043811</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>01097910906</t>
+          <t>01037904341</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>280909</t>
+          <t>307164</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>bizboard</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>kk_2788293490</t>
+          <t>kk_3840423259</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>01052092586</t>
+          <t>01050355480</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>209979</t>
+          <t>264298</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>kk_4929043811</t>
+          <t>passion1984</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>01037904341</t>
+          <t>01064630333</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>307164</t>
+          <t>264683</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>bizboard</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>kk_3840423259</t>
+          <t>rudalsla</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>01050355480</t>
+          <t>01071949782</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>264298</t>
+          <t>306362</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -709,78 +709,78 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>passion1984</t>
+          <t>kk_5053218420</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>01064630333</t>
+          <t>01053426954</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>264683</t>
+          <t>311746</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>rudalsla</t>
+          <t>skku2738</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>01071949782</t>
+          <t>01074152738</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>306362</t>
+          <t>35128</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kk_5053218420</t>
+          <t>gbj20022002</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>01053426954</t>
+          <t>01053509041</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>311746</t>
+          <t>53032</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -790,51 +790,51 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>skku2738</t>
+          <t>kk_3433423317</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>01074152738</t>
+          <t>01075326556</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>35128</t>
+          <t>242341</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>gbj20022002</t>
+          <t>hjb007</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>01053509041</t>
+          <t>01096664026</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>53032</t>
+          <t>144397</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -844,51 +844,51 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>kk_2783594999</t>
+          <t>poweryys</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>01095317357</t>
+          <t>01089678835</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>209807</t>
+          <t>214318</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>[PF]A+SC_상시(1865MF,논타겟)</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>kk_3433423317</t>
+          <t>kk_5034001705</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>01075326556</t>
+          <t>01090601731</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>242341</t>
+          <t>311133</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -898,24 +898,24 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>hjb007</t>
+          <t>kk_5046820175</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>01096664026</t>
+          <t>01062781955</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>144397</t>
+          <t>311563</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -925,24 +925,24 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>방문_하이브리드 오디언스</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>poweryys</t>
+          <t>kk_3407332090</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>01089678835</t>
+          <t>01073480423</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>214318</t>
+          <t>241393</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -952,24 +952,24 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>kk_5034001705</t>
+          <t>honor181</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>01090601731</t>
+          <t>01046301211</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>311133</t>
+          <t>192770</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -979,24 +979,24 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>kk_5046820175</t>
+          <t>limsoo1719</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>01062781955</t>
+          <t>01055751719</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>311563</t>
+          <t>84759</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1006,24 +1006,24 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>방문_하이브리드 오디언스</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>kk_3407332090</t>
+          <t>jpm111</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>01073480423</t>
+          <t>01029304010</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>241393</t>
+          <t>249216</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1033,24 +1033,24 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>honor181</t>
+          <t>kk_4973864658</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>01046301211</t>
+          <t>01023113061</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>192770</t>
+          <t>308691</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1060,78 +1060,78 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>방문_하이브리드 오디언스</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>limsoo1719</t>
+          <t>kk_3184721081</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>01055751719</t>
+          <t>01085470105</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>84759</t>
+          <t>229171</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>KAKAO_CH_MENU_0209_NEWYEAR</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>jpm111</t>
+          <t>swsun9</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>01029304010</t>
+          <t>01097889718</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>249216</t>
+          <t>295157</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>kk_4973864658</t>
+          <t>sky2446</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>01023113061</t>
+          <t>01086189169</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>308691</t>
+          <t>310077</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1141,24 +1141,24 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>방문_하이브리드 오디언스</t>
+          <t>da</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>kk_3184721081</t>
+          <t>kk_3697411135</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>01085470105</t>
+          <t>01074605090</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>229171</t>
+          <t>251206</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1168,51 +1168,51 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0209_NEWYEAR</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>swsun9</t>
+          <t>thebebob</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>01097889718</t>
+          <t>01094365308</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>295157</t>
+          <t>196123</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>sky2446</t>
+          <t>sooenter2021</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>01086189169</t>
+          <t>01051830725</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>310077</t>
+          <t>310304</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1222,159 +1222,159 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>kk_3697411135</t>
+          <t>kk_3775635739</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>01074605090</t>
+          <t>01047873237</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>251206</t>
+          <t>255851</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>[PF]A+SC_상시(1865MF,논타겟)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>thebebob</t>
+          <t>kk_3147981567</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>01094365308</t>
+          <t>01072033421</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>196123</t>
+          <t>223217</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_CH_MENU_0702_REVERSEDOWN</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>sooenter2021</t>
+          <t>kk_4209546622</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>01051830725</t>
+          <t>01079193288</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>310304</t>
+          <t>272272</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>kk_3775635739</t>
+          <t>kk_4315111161</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>01047873237</t>
+          <t>01080806591</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>255851</t>
+          <t>277461</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>[PF]A+SC_상시(1865MF,논타겟)</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>kk_3147981567</t>
+          <t>jakelee</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>01072033421</t>
+          <t>01027223531</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>223217</t>
+          <t>16193</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0702_REVERSEDOWN</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>kk_4209546622</t>
+          <t>kk_4647481524</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>01079193288</t>
+          <t>01030569095</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>272272</t>
+          <t>292864</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1391,44 +1391,44 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>kk_4315111161</t>
+          <t>hajd1011</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>01080806591</t>
+          <t>01054401373</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>277461</t>
+          <t>283249</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>jakelee</t>
+          <t>kk_5008721553</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>01027223531</t>
+          <t>01089905677</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>16193</t>
+          <t>310248</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1438,24 +1438,24 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>kk_4647481524</t>
+          <t>arrtieom</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>01030569095</t>
+          <t>01071593949</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>292864</t>
+          <t>141170</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1465,24 +1465,24 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>KAKAO_CH_MESSAGE_0521_BAHAMA1</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>hajd1011</t>
+          <t>kk_4615977966</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>01054401373</t>
+          <t>01029473782</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>283249</t>
+          <t>290690</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1499,17 +1499,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>kk_5008721553</t>
+          <t>kk_4516410827</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>01089905677</t>
+          <t>01048475313</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>310248</t>
+          <t>285997</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1519,105 +1519,105 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>da</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>kk_2807327385</t>
+          <t>kk_5036115734</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>01038584194</t>
+          <t>01046709214</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>211579</t>
+          <t>311217</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>arrtieom</t>
+          <t>kk_2751892064_2</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>01071593949</t>
+          <t>01044569101</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>141170</t>
+          <t>282142</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0521_BAHAMA1</t>
+          <t>[PF]전환_상시(2565MF,비구매자30일)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>kk_4615977966</t>
+          <t>lbw1427</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>01029473782</t>
+          <t>01050283447</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>290690</t>
+          <t>23189</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>kk_4516410827</t>
+          <t>kk_5048808976</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>01048475313</t>
+          <t>01026908279</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>285997</t>
+          <t>311623</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1627,29 +1627,29 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>kk_5036115734</t>
+          <t>kk_4940334145</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>01046709214</t>
+          <t>01025490108</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>311217</t>
+          <t>307549</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1661,152 +1661,152 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>kk_2751892064_2</t>
+          <t>kk_4387186836</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>01044569101</t>
+          <t>01085670209</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>282142</t>
+          <t>280506</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자30일)</t>
+          <t>0716_SEASON_OFF_2ND</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>lbw1427</t>
+          <t>romanohong</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>01050283447</t>
+          <t>01089301124</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>23189</t>
+          <t>32607</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>0520</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>kk_5048808976</t>
+          <t>uofnywam</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>01026908279</t>
+          <t>01025062538</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>311623</t>
+          <t>204156</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>kk_4940334145</t>
+          <t>kk_3216728258</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>01025490108</t>
+          <t>01082974119</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>307549</t>
+          <t>232259</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>sow9952</t>
+          <t>chokiwbang</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>01035936872</t>
+          <t>01052258818</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>133707</t>
+          <t>140204</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>kk_3336020425</t>
+          <t>kk_4468049816</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>01092551720</t>
+          <t>01079335600</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>238889</t>
+          <t>283582</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1816,78 +1816,78 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0818_BRANDTALK_JONAS</t>
+          <t>KAKAO_CH_MESSAGE_0226_BTS</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>kk_3224620899</t>
+          <t>kk_5050299156</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>01085627400</t>
+          <t>01026976598</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>232942</t>
+          <t>311666</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>kk_4666532522</t>
+          <t>naroo27</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>01052618464</t>
+          <t>01075300052</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>294012</t>
+          <t>102129</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>LMS_ECOM_0425_FAMILYSALE</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>kk_4387186836</t>
+          <t>ugjina</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>01085670209</t>
+          <t>01065057791</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>280506</t>
+          <t>242092</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1897,24 +1897,24 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0716_SEASON_OFF_2ND</t>
+          <t>0622</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>romanohong</t>
+          <t>kk_3179837389</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>01089301124</t>
+          <t>01089490421</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>32607</t>
+          <t>225507</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1924,24 +1924,24 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0520</t>
+          <t>0803_SUMMER_LAST_CHANCE</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>uofnywam</t>
+          <t>kk_4582648301</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>01025062538</t>
+          <t>01040451815</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>204156</t>
+          <t>288564</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1951,132 +1951,132 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>kk_3216728258</t>
+          <t>aceykh</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>01082974119</t>
+          <t>01041402352</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>232259</t>
+          <t>140002</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>EDM_TOP</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>chokiwbang</t>
+          <t>kk_3849010182</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>01052258818</t>
+          <t>01071058942</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>140204</t>
+          <t>264944</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>etc</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>kk_4270789121</t>
+          <t>kk_4481940140</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>01088030339</t>
+          <t>01065676272</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>274863</t>
+          <t>284338</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>bizboard</t>
+          <t>[PF_SA] 컬럼비아 상시</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>kk_4468049816</t>
+          <t>aaeolus</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>01079335600</t>
+          <t>01082605032</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>283582</t>
+          <t>282510</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0226_BTS</t>
+          <t>etc</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>kk_5050299156</t>
+          <t>kk_3769382715</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>01026976598</t>
+          <t>01098220944</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>311666</t>
+          <t>255392</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2086,24 +2086,24 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>naroo27</t>
+          <t>kk_3801004682</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>01075300052</t>
+          <t>01024159216</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>102129</t>
+          <t>258930</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2113,78 +2113,78 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0425_FAMILYSALE</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>polarisshine</t>
+          <t>kk_3772986666</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>01033610394</t>
+          <t>01085470459</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>241319</t>
+          <t>255687</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ugjina</t>
+          <t>herowill</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>01065057791</t>
+          <t>01088996520</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>242092</t>
+          <t>85660</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0622</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>kk_3179837389</t>
+          <t>wnsvy2957</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>01089490421</t>
+          <t>01052632952</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>225507</t>
+          <t>283008</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2194,24 +2194,24 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0803_SUMMER_LAST_CHANCE</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>kk_4582648301</t>
+          <t>kk_3182977787</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>01040451815</t>
+          <t>01085398119</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>288564</t>
+          <t>228089</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2228,44 +2228,44 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>kk_3774156950</t>
+          <t>kk_2845811024_3</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>01041159966</t>
+          <t>01083771174</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>255778</t>
+          <t>307634</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>aceykh</t>
+          <t>kk_3047832258</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>01041402352</t>
+          <t>01053403023</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>140002</t>
+          <t>220442</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2275,105 +2275,105 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>EDM_TOP</t>
+          <t>EDM_0329</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>kk_3849010182</t>
+          <t>kk_4319247532</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>01071058942</t>
+          <t>01088594122</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>264944</t>
+          <t>277718</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>kk_4481940140</t>
+          <t>potanion</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>01065676272</t>
+          <t>01027653082</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>284338</t>
+          <t>215442</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>[PF_SA] 컬럼비아 상시</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>aaeolus</t>
+          <t>kk_5053571972</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>01082605032</t>
+          <t>01062303845</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>282510</t>
+          <t>311761</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>kk_3769382715</t>
+          <t>kk_5041074251</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>01098220944</t>
+          <t>01058983349</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>255392</t>
+          <t>311361</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2383,51 +2383,51 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>120253016536170385</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>kk_5034366506</t>
+          <t>tmdwosnsk</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>01027228694</t>
+          <t>01040847350</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>311148</t>
+          <t>239452</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>방문_하이브리드 오디언스</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>kk_3801004682</t>
+          <t>kk_3099382486</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>01024159216</t>
+          <t>01093078148</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>258930</t>
+          <t>221525</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2437,78 +2437,78 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>kk_3772986666</t>
+          <t>kk_5054179034</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>01085470459</t>
+          <t>01066850120</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>255687</t>
+          <t>311781</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>herowill</t>
+          <t>kk_4997974077</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>01088996520</t>
+          <t>01040095693</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>85660</t>
+          <t>309775</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>wnsvy2957</t>
+          <t>yk8809</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>01052632952</t>
+          <t>01023568809</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>283008</t>
+          <t>199548</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2518,24 +2518,24 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>kk_4305413789</t>
+          <t>leek78910</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>01091584326</t>
+          <t>01054949937</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>276813</t>
+          <t>211793</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2545,159 +2545,159 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>0610</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>kk_3182977787</t>
+          <t>dyckim</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>01085398119</t>
+          <t>01044401262</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>228089</t>
+          <t>310573</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>kk_2845811024_3</t>
+          <t>kk_5051879020</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>01083771174</t>
+          <t>01071731874</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>307634</t>
+          <t>311712</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>da</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>kk_3047832258</t>
+          <t>itsuky3785</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>01053403023</t>
+          <t>01033352103</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>220442</t>
+          <t>288167</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>EDM_0329</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>kk_4319247532</t>
+          <t>khs0905</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>01088594122</t>
+          <t>01076640154</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>277718</t>
+          <t>137732</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>potanion</t>
+          <t>nada1989</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>01027653082</t>
+          <t>01089413334</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>215442</t>
+          <t>203214</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>kk_5053571972</t>
+          <t>kys6181</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>01062303845</t>
+          <t>01065450817</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>311761</t>
+          <t>196299</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2714,17 +2714,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>kk_5041074251</t>
+          <t>kk_4303259863</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>01058983349</t>
+          <t>01088772815</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>311361</t>
+          <t>276683</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2734,24 +2734,24 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>120253016536170385</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>kk_3166677890</t>
+          <t>kk_5010416607</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>01032440825</t>
+          <t>01089512927</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>224642</t>
+          <t>310314</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2761,132 +2761,132 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>0520</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>tmdwosnsk</t>
+          <t>kk_3111973500</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>01040847350</t>
+          <t>01064187132</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>239452</t>
+          <t>267677</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>kk_3099382486</t>
+          <t>redsuede</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>01093078148</t>
+          <t>01032879838</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>221525</t>
+          <t>273348</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>kk_5054179034</t>
+          <t>kk_5052884183</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>01066850120</t>
+          <t>01030388284</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>311781</t>
+          <t>311732</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naversa_pc</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>kk_4997974077</t>
+          <t>kk_5053135733</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>01040095693</t>
+          <t>01062083028</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>309775</t>
+          <t>311742</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>yk8809</t>
+          <t>kk_4671019003</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>01023568809</t>
+          <t>01064700873</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>199548</t>
+          <t>294341</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2896,24 +2896,24 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>leek78910</t>
+          <t>kk_5049890573</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>01054949937</t>
+          <t>01094328346</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>211793</t>
+          <t>311657</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -2923,105 +2923,105 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>0610</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>dyckim</t>
+          <t>kk_5051471907</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>01044401262</t>
+          <t>01092552888</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>310573</t>
+          <t>311705</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>kk_5051879020</t>
+          <t>kk_5053813602</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>01071731874</t>
+          <t>01094931734</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>311712</t>
+          <t>311771</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>etc</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>itsuky3785</t>
+          <t>h11145</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>01033352103</t>
+          <t>01073342519</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>288167</t>
+          <t>311682</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>방문_하이브리드 오디언스</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>khs0905</t>
+          <t>kk_5052996890</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>01076640154</t>
+          <t>01028467527</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>137732</t>
+          <t>311736</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3031,24 +3031,24 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>etc</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>amalpi12</t>
+          <t>kk_4830179048</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>01053261363</t>
+          <t>01059171953</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>108484</t>
+          <t>303507</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3058,51 +3058,51 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>naversa_mo</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>nada1989</t>
+          <t>bubbo7942</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>01089413334</t>
+          <t>01041446001</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>203214</t>
+          <t>311654</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>방문_하이브리드 오디언스</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>kys6181</t>
+          <t>hhgg6482</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>01065450817</t>
+          <t>01052195642</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>196299</t>
+          <t>290916</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3112,51 +3112,51 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>kk_5048734886</t>
+          <t>sclpion</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>01056134824</t>
+          <t>01088740653</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>311621</t>
+          <t>141669</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>kk_4303259863</t>
+          <t>gogo4135</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>01088772815</t>
+          <t>01088831877</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>276683</t>
+          <t>170683</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3166,132 +3166,132 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>kk_5010416607</t>
+          <t>fcozy</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>01089512927</t>
+          <t>01083998861</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>310314</t>
+          <t>114021</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>kk_3805575606</t>
+          <t>kk_5052989693</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>01025333198</t>
+          <t>01095421888</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>260080</t>
+          <t>311735</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자30일)</t>
+          <t>etc</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>kk_3111973500</t>
+          <t>lees0925</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>01064187132</t>
+          <t>01089944951</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>267677</t>
+          <t>284991</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>redsuede</t>
+          <t>kk_5053146625</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>01032879838</t>
+          <t>01092265566</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>273348</t>
+          <t>311743</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>etc</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>kk_5052884183</t>
+          <t>kk_5040443935</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>01030388284</t>
+          <t>01086507863</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>311732</t>
+          <t>311339</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3301,24 +3301,24 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>naversa_pc</t>
+          <t>[PF]전환_상시(2565MF,비구매자30일)</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>kk_5053135733</t>
+          <t>he2008417</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>01062083028</t>
+          <t>01091680417</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>311742</t>
+          <t>153431</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3335,71 +3335,71 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>kk_4671019003</t>
+          <t>kk_5050610678</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>01064700873</t>
+          <t>01093820086</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>294341</t>
+          <t>311678</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>kk_5049890573</t>
+          <t>yuna8819</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>01094328346</t>
+          <t>01027098819</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>311657</t>
+          <t>278063</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>0705_SEASON_OFF_2ND</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>kk_4525960790</t>
+          <t>kk_5049571823</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>01084170327</t>
+          <t>01063482295</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>286541</t>
+          <t>311646</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -3409,51 +3409,51 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>방문_하이브리드 오디언스</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>kk_5047910275</t>
+          <t>russia55</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>01092819854</t>
+          <t>01022813614</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>311600</t>
+          <t>170004</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>kk_5051471907</t>
+          <t>molgue</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>01092552888</t>
+          <t>01096385787</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>311705</t>
+          <t>189580</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -3463,132 +3463,132 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>방문_하이브리드 오디언스</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>kk_5053813602</t>
+          <t>kk_4234730563</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>01094931734</t>
+          <t>01072748373</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>311771</t>
+          <t>273531</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>h11145</t>
+          <t>piung8</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>01073342519</t>
+          <t>01024302128</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>311682</t>
+          <t>241561</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>방문_하이브리드 오디언스</t>
+          <t>da</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>kk_5052996890</t>
+          <t>kk_5053573200</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>01028467527</t>
+          <t>01050217981</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>311736</t>
+          <t>311762</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>kk_4462645892</t>
+          <t>kk_2794341634</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>01032388020</t>
+          <t>01062258622</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>283222</t>
+          <t>210525</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0728_OMNISHADE</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>kk_4830179048</t>
+          <t>humi312</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>01059171953</t>
+          <t>01032018321</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>303507</t>
+          <t>109372</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -3598,105 +3598,105 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>방문_하이브리드 오디언스</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ybk636</t>
+          <t>kk_3392066640</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>01093437733</t>
+          <t>01065021283</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>192859</t>
+          <t>240983</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>kjc9408</t>
+          <t>kk_3140884947</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>01047170394</t>
+          <t>01081538888</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>112828</t>
+          <t>222841</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>0818_BRANDTALK_JONAS</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>bubbo7942</t>
+          <t>kk_4445795434</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>01041446001</t>
+          <t>01027315428</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>311654</t>
+          <t>282265</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>방문_하이브리드 오디언스</t>
+          <t>0803_Clearance</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>hhgg6482</t>
+          <t>mupasa1010</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>01052195642</t>
+          <t>01098195600</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>290916</t>
+          <t>197579</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -3706,24 +3706,24 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>oh8314</t>
+          <t>drunkenly</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>01090595921</t>
+          <t>01047087372</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>222937</t>
+          <t>182608</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -3733,24 +3733,24 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>lf</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>sclpion</t>
+          <t>kk_4967367828</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>01088740653</t>
+          <t>01090955298</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>141669</t>
+          <t>308392</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -3760,267 +3760,267 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>gogo4135</t>
+          <t>icoram</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>01088831877</t>
+          <t>01091898092</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>170683</t>
+          <t>311807</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>fcozy</t>
+          <t>kk_3222864535</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>01083998861</t>
+          <t>01087438761</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>114021</t>
+          <t>232810</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>kk_5052989693</t>
+          <t>della96</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>01095421888</t>
+          <t>01071782565</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>311735</t>
+          <t>119198</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>방문_하이브리드 오디언스</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>song0392</t>
+          <t>kk_5052196631</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>01090885015</t>
+          <t>01035951351</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>281019</t>
+          <t>311723</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>lees0925</t>
+          <t>kk_4915210068</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>01089944951</t>
+          <t>01054111693</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>284991</t>
+          <t>306647</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>kk_5053146625</t>
+          <t>kk_4286220576</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>01092265566</t>
+          <t>01053587782</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>311743</t>
+          <t>275624</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>LMS_ECOM_200416_seasonoff</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>kk_5040443935</t>
+          <t>kk_2919185721</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>01086507863</t>
+          <t>01034872320</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>311339</t>
+          <t>215776</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자30일)</t>
+          <t>etc</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>dearmyjack</t>
+          <t>kk_4213116180</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>01043663669</t>
+          <t>01094956022</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>136045</t>
+          <t>272450</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKO_CH_MESSAGE_0817_SUMMERCLEARANCE</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>he2008417</t>
+          <t>ghffhs</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>01091680417</t>
+          <t>01086461880</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>153431</t>
+          <t>172816</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>kk_5050610678</t>
+          <t>hiyeom</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>01093820086</t>
+          <t>01092193123</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>311678</t>
+          <t>73820</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -4030,213 +4030,213 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>da</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>yuna8819</t>
+          <t>kk_3211764926</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>01027098819</t>
+          <t>01065592320</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>278063</t>
+          <t>231794</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>0705_SEASON_OFF_2ND</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>kk_5049571823</t>
+          <t>jsy90</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>01063482295</t>
+          <t>01055153689</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>311646</t>
+          <t>304378</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>방문_하이브리드 오디언스</t>
+          <t>LMS_ECOM_0410pants2</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>russia55</t>
+          <t>kk_3923084698</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>01022813614</t>
+          <t>01093992638</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>170004</t>
+          <t>268693</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>kk_3659391806</t>
+          <t>kk_4902163917</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>01065644929</t>
+          <t>01091388108</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>249571</t>
+          <t>306260</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>kk_3602653890</t>
+          <t>kk_5050813376</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>01077530445</t>
+          <t>01032764500</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>247108</t>
+          <t>311685</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>0818_BRANDTALK_JONAS</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>molgue</t>
+          <t>kk_5054290902</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>01096385787</t>
+          <t>01089708874</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>189580</t>
+          <t>311785</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>방문_하이브리드 오디언스</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>kk_4234730563</t>
+          <t>kk_5049435171</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>01072748373</t>
+          <t>01082504237</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>273531</t>
+          <t>311643</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>etc</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>piung8</t>
+          <t>kkk570908</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>01024302128</t>
+          <t>01037997125</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>241561</t>
+          <t>268558</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -4253,71 +4253,71 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>kk_3158724749</t>
+          <t>kk_3415923718</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>01093699572</t>
+          <t>01087476815</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>223942</t>
+          <t>241616</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>da</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>kk_2931375451</t>
+          <t>younghee1c</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>01091147926</t>
+          <t>01045678561</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>216087</t>
+          <t>174797</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKO_CH_MESSAGE_0817_SUMMERCLEARANCE</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>kk_5053573200</t>
+          <t>kk_4667580040</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>01050217981</t>
+          <t>01097556194</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>311762</t>
+          <t>294108</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -4327,51 +4327,51 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>kk_2794341634</t>
+          <t>younge789</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>01062258622</t>
+          <t>01085185168</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>210525</t>
+          <t>169078</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>humi312</t>
+          <t>kk_5054464771</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>01032018321</t>
+          <t>01087583944</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>109372</t>
+          <t>311791</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -4381,51 +4381,51 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>방문_하이브리드 오디언스</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>kk_3392066640</t>
+          <t>kk_3157182568</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>01065021283</t>
+          <t>01057620105</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>240983</t>
+          <t>223820</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>kk_3140884947</t>
+          <t>happyglory81</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>01081538888</t>
+          <t>01064760332</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>222841</t>
+          <t>135652</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -4435,24 +4435,24 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>0818_BRANDTALK_JONAS</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>cek9920</t>
+          <t>kk_5052645690</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>01090616068</t>
+          <t>01094486334</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>272152</t>
+          <t>311729</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -4469,179 +4469,179 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>kk_4445795434</t>
+          <t>kk_5054057588</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>01027315428</t>
+          <t>01047332261</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>282265</t>
+          <t>311778</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>0803_Clearance</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>mupasa1010</t>
+          <t>kk_4288755561</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>01098195600</t>
+          <t>01042420896</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>197579</t>
+          <t>275791</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKO_CH_MESSAGE_0817_TRAILRUN</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>drunkenly</t>
+          <t>kk_3170595620</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>01047087372</t>
+          <t>01027919785</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>182608</t>
+          <t>224951</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>kk_4967367828</t>
+          <t>kk_3303914582</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>01090955298</t>
+          <t>01028715525</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>308392</t>
+          <t>237924</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>kk_3884244178</t>
+          <t>kk_5050311909</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>01022212144</t>
+          <t>01039067015</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>267070</t>
+          <t>311667</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_CH_MENU_0728_AMBASSADOR</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>icoram</t>
+          <t>kk_5046654259</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>01091898092</t>
+          <t>01054946646</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>311807</t>
+          <t>311556</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>da</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>kk_3222864535</t>
+          <t>daekwangsu</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>01087438761</t>
+          <t>01055970579</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>232810</t>
+          <t>96203</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -4658,17 +4658,17 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>jindol7979</t>
+          <t>kk_3622891451</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>01057673106</t>
+          <t>01053726280</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>248350</t>
+          <t>247735</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -4678,294 +4678,294 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>della96</t>
+          <t>kk_3842461525</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>01071782565</t>
+          <t>01077300704</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>119198</t>
+          <t>264453</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>방문_하이브리드 오디언스</t>
+          <t>0520</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>kk_5052196631</t>
+          <t>merhen</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>01035951351</t>
+          <t>01025129134</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>311723</t>
+          <t>89491</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>kk_4915210068</t>
+          <t>kk_3728610953</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>01054111693</t>
+          <t>01092914950</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>306647</t>
+          <t>252762</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>kk_4286220576</t>
+          <t>gusrb5315</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>01053587782</t>
+          <t>01033445315</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>275624</t>
+          <t>240662</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>LMS_ECOM_200416_seasonoff</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>kk_2919185721</t>
+          <t>kk_5053760478</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>01034872320</t>
+          <t>01025944738</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>215776</t>
+          <t>311768</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>kk_4213116180</t>
+          <t>ic8871</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>01094956022</t>
+          <t>01063456741</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>272450</t>
+          <t>117110</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>KAKO_CH_MESSAGE_0817_SUMMERCLEARANCE</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ghffhs</t>
+          <t>kk_3700715231</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>01086461880</t>
+          <t>01033535653</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>172816</t>
+          <t>251354</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>hiyeom</t>
+          <t>sm297</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>01092193123</t>
+          <t>01089954070</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>73820</t>
+          <t>172466</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>etc</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>kk_3211764926</t>
+          <t>sunam12</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>01065592320</t>
+          <t>01081404180</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>231794</t>
+          <t>148548</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_MESSAGE_260702_SEASONOFF2ND</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>jsy90</t>
+          <t>soleado</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>01055153689</t>
+          <t>01067078981</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>304378</t>
+          <t>289679</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410pants2</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>kk_3923084698</t>
+          <t>kk_3035383266</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>01093992638</t>
+          <t>01036728869</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>268693</t>
+          <t>219867</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -4975,24 +4975,24 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>kk_5048056578</t>
+          <t>wjddmsp4</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>01026160032</t>
+          <t>01027170361</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>311606</t>
+          <t>103841</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -5002,78 +5002,78 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>[PF]A+SC_상시(논타겟)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>nikemkr</t>
+          <t>kk_5001853528</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>01032361592</t>
+          <t>01063062373</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>145423</t>
+          <t>309969</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>[PF]A+SC_상시(논타겟)</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>kk_4902163917</t>
+          <t>kk_4442668340</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>01091388108</t>
+          <t>01089979956</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>306260</t>
+          <t>282163</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>etc</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>kk_3905070874</t>
+          <t>fjqm1717</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>01089213133</t>
+          <t>01093376905</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>267935</t>
+          <t>185768</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -5083,105 +5083,105 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_260702_SEASONOFF2ND</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>kk_5050813376</t>
+          <t>kk_4679174258</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>01032764500</t>
+          <t>01054503197</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>311685</t>
+          <t>294810</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>kk_5054290902</t>
+          <t>kk_5053440830</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>01089708874</t>
+          <t>01075725067</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>311785</t>
+          <t>311758</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>방문_하이브리드 오디언스</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>kk_5049435171</t>
+          <t>kk_5026095899</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>01082504237</t>
+          <t>01086935544</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>311643</t>
+          <t>310852</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>kkk570908</t>
+          <t>mgoon1005</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>01037997125</t>
+          <t>01054720108</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>268558</t>
+          <t>266467</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -5191,51 +5191,51 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>kk_3415923718</t>
+          <t>kk_3666720704</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>01087476815</t>
+          <t>01033458251</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>241616</t>
+          <t>249880</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>KAKAO_CH_MESSAGE_260702_WATERPROOFITEM</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>younghee1c</t>
+          <t>apple9420</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>01045678561</t>
+          <t>01062379420</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>174797</t>
+          <t>256551</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -5245,51 +5245,51 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>KAKO_CH_MESSAGE_0817_SUMMERCLEARANCE</t>
+          <t>0803_Clearance</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>kk_4667580040</t>
+          <t>kk_3733604305</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>01097556194</t>
+          <t>01046180063</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>294108</t>
+          <t>253138</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>KAKAO_CH_MESSAGE_0730_OMNISHADE</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>younge789</t>
+          <t>dbeodus12</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>01085185168</t>
+          <t>01094952956</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>169078</t>
+          <t>177779</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -5306,71 +5306,71 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>kk_3651374600</t>
+          <t>kk_5025530724</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>01022677229</t>
+          <t>01055050266</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>249194</t>
+          <t>310814</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>kk_5048020264</t>
+          <t>kk_4442439433</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>01050643628</t>
+          <t>01075664837</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>311602</t>
+          <t>282157</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>방문_하이브리드 오디언스</t>
+          <t>0520</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>kk_4427917124</t>
+          <t>bluesung226</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>01087800644</t>
+          <t>01024421910</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>281608</t>
+          <t>205476</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -5380,294 +5380,294 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>0818_BRANDTALK_JONAS</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>kk_5054464771</t>
+          <t>kk_5001280835</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>01087583944</t>
+          <t>01088193949</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>311791</t>
+          <t>309942</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>kk_3157182568</t>
+          <t>kk_3168093587</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>01057620105</t>
+          <t>01087964559</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>223820</t>
+          <t>224737</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>kk_3913904307</t>
+          <t>kk_5054226033</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>01043366180</t>
+          <t>01084058475</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>268347</t>
+          <t>311784</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>cutys85</t>
+          <t>june715</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>01091304218</t>
+          <t>01071157671</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>131238</t>
+          <t>172897</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_MENU_260603_SEASONOFF</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>sjkimamp</t>
+          <t>kk_5052086920</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>01020527626</t>
+          <t>01087726668</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>311558</t>
+          <t>311718</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>etc</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>kk_5037350027</t>
+          <t>kk_3810304670</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>01054100445</t>
+          <t>01041348052</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>311256</t>
+          <t>261190</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_200416_family</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>happyglory81</t>
+          <t>kk_3372478035</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>01064760332</t>
+          <t>01073318137</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>135652</t>
+          <t>240206</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>kk_5052645690</t>
+          <t>seomina0907</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>01094486334</t>
+          <t>01094631272</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>311729</t>
+          <t>166015</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>kk_5049352857</t>
+          <t>kk_5053805303</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>01049105100</t>
+          <t>01035199923</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>311639</t>
+          <t>311769</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>kk_5054057588</t>
+          <t>bambae74</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>01047332261</t>
+          <t>01037840714</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>311778</t>
+          <t>68767</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>da</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>kk_4288755561</t>
+          <t>jscho01</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>01042420896</t>
+          <t>01053208316</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>275791</t>
+          <t>139260</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -5677,186 +5677,186 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>KAKO_CH_MESSAGE_0817_TRAILRUN</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>thlation</t>
+          <t>playalone74</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>01023085363</t>
+          <t>01052891032</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>155504</t>
+          <t>169585</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>kk_5048053752</t>
+          <t>kk_4977819786</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>01045063197</t>
+          <t>01063257991</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>311605</t>
+          <t>308849</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>kk_3170595620</t>
+          <t>cej0422</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>01027919785</t>
+          <t>01059680246</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>224951</t>
+          <t>308449</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>kk_3303914582</t>
+          <t>kk_4824182622</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>01028715525</t>
+          <t>01098590199</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>237924</t>
+          <t>303158</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>kk_5050311909</t>
+          <t>kk_5050508246</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>01039067015</t>
+          <t>01099167304</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>311667</t>
+          <t>311676</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0728_AMBASSADOR</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>kk_5046654259</t>
+          <t>dhk1827</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>01054946646</t>
+          <t>01027971827</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>311556</t>
+          <t>286842</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>kk_5048447451</t>
+          <t>kk_2846130578</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>01090199835</t>
+          <t>01064075652</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>311616</t>
+          <t>213236</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -5866,78 +5866,78 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>120253016536170385</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>ghd8488</t>
+          <t>kk_4279643731</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>01085019609</t>
+          <t>01094073928</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>114774</t>
+          <t>275243</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>6941110100332</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>daekwangsu</t>
+          <t>kk_5029461637</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>01055970579</t>
+          <t>01037759598</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>96203</t>
+          <t>310962</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>kk_4725433749</t>
+          <t>yan01062</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>01096687926</t>
+          <t>01076707692</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>297917</t>
+          <t>203357</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -5947,132 +5947,132 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>kk_3622891451</t>
+          <t>kk_3163403095</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>01053726280</t>
+          <t>01094442663</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>247735</t>
+          <t>224415</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKO_CH_MESSAGE_0817_SUMMERCLEARANCE</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>kk_3842461525</t>
+          <t>kk_5054920254</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>01077300704</t>
+          <t>01093769998</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>264453</t>
+          <t>311799</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>0520</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>merhen</t>
+          <t>kk_5055001343</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>01025129134</t>
+          <t>01047875895</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>89491</t>
+          <t>311801</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>kk_3728610953</t>
+          <t>kk_3685066575</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>01092914950</t>
+          <t>01021696118</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>252762</t>
+          <t>250622</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>kk_3184880563</t>
+          <t>wasserland</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>01098981647</t>
+          <t>01051765220</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>229252</t>
+          <t>177860</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -6082,132 +6082,132 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>gusrb5315</t>
+          <t>kk_3180692048</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>01033445315</t>
+          <t>01046133289</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>240662</t>
+          <t>226239</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>kk_5053760478</t>
+          <t>kk_5052988564</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>01025944738</t>
+          <t>01047680429</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>311768</t>
+          <t>311734</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>ic8871</t>
+          <t>kk_3306066072</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>01063456741</t>
+          <t>01048303593</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>117110</t>
+          <t>238116</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>kk_5047948726</t>
+          <t>kk_5049869649</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>01052279069</t>
+          <t>01051240904</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>311601</t>
+          <t>311655</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>kk_3700715231</t>
+          <t>djae63</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>01033535653</t>
+          <t>01027633204</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>251354</t>
+          <t>245415</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -6217,159 +6217,159 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>kk_5046995403</t>
+          <t>kk_3864552155</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>01088979860</t>
+          <t>01035193074</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>311569</t>
+          <t>265863</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>sm297</t>
+          <t>kk_5052479419</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>01089954070</t>
+          <t>01047117155</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>172466</t>
+          <t>311726</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>sunam12</t>
+          <t>hawol10041</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>01081404180</t>
+          <t>01066458661</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>148548</t>
+          <t>311107</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_260702_SEASONOFF2ND</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>soleado</t>
+          <t>kk_2867961634</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>01067078981</t>
+          <t>01033939933</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>289679</t>
+          <t>213870</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>kk_3035383266</t>
+          <t>kk_5053401059</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>01036728869</t>
+          <t>01021051426</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>219867</t>
+          <t>311756</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>wjddmsp4</t>
+          <t>gigsfree</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>01027170361</t>
+          <t>01088779997</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>103841</t>
+          <t>56427</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -6386,17 +6386,17 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>kk_5001853528</t>
+          <t>kkjjg123</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>01063062373</t>
+          <t>01036960451</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>309969</t>
+          <t>110344</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -6406,213 +6406,213 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>[PF]A+SC_상시(논타겟)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>kk_4442668340</t>
+          <t>kk_5053312014</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>01089979956</t>
+          <t>01076680710</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>282163</t>
+          <t>311750</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>fjqm1717</t>
+          <t>seep</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>01093376905</t>
+          <t>01051600565</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>185768</t>
+          <t>112406</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>kk_4679174258</t>
+          <t>kk_5050922316</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>01054503197</t>
+          <t>01046206459</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>294810</t>
+          <t>311689</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>kk_5053440830</t>
+          <t>son2245</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>01075725067</t>
+          <t>01039192245</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>311758</t>
+          <t>164240</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>방문_하이브리드 오디언스</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>kk_5026095899</t>
+          <t>kk_5055289049</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>01086935544</t>
+          <t>01029088281</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>310852</t>
+          <t>311808</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>mgoon1005</t>
+          <t>kk_5050974529</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>01054720108</t>
+          <t>01023991588</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>266467</t>
+          <t>311692</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>KAKO_CH_MESSAGE_0817_SUMMERCLEARANCE</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>won8793</t>
+          <t>kk_3476177906</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>01045906843</t>
+          <t>01079305414</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>102019</t>
+          <t>244235</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>kk_3666720704</t>
+          <t>kk_3723340115</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>01033458251</t>
+          <t>01088904849</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>249880</t>
+          <t>252352</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -6622,78 +6622,78 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_260702_WATERPROOFITEM</t>
+          <t>KAKO_CH_MESSAGE_0817_SUMMERCLEARANCE</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>apple9420</t>
+          <t>kk_5049789835</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>01062379420</t>
+          <t>01094739795</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>256551</t>
+          <t>311653</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>0803_Clearance</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>kk_3733604305</t>
+          <t>lss7705</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>01046180063</t>
+          <t>01041147448</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>253138</t>
+          <t>237569</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0730_OMNISHADE</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>dbeodus12</t>
+          <t>kk_5050552723</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>01094952956</t>
+          <t>01050032168</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>177779</t>
+          <t>311677</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -6710,125 +6710,125 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>kk_5025530724</t>
+          <t>minjin6789</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>01055050266</t>
+          <t>01024062050</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>310814</t>
+          <t>157791</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>kk_4442439433</t>
+          <t>kk_3626416291</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>01075664837</t>
+          <t>01049003915</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>282157</t>
+          <t>247860</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>0520</t>
+          <t>etc</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>bluesung226</t>
+          <t>kk_5054844830</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>01024421910</t>
+          <t>01025386330</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>205476</t>
+          <t>311796</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>kk_5001280835</t>
+          <t>kk_5053032122</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>01088193949</t>
+          <t>01053783882</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>309942</t>
+          <t>311739</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>kk_3168093587</t>
+          <t>kk_5053223845</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>01087964559</t>
+          <t>01096775572</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>224737</t>
+          <t>311747</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -6838,105 +6838,105 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>da</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>kk_5054226033</t>
+          <t>kk_3156778149</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>01084058475</t>
+          <t>01084700197</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>311784</t>
+          <t>223775</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>kk_5052086920</t>
+          <t>priscus</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>01087726668</t>
+          <t>01083762352</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>311718</t>
+          <t>105660</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>june715</t>
+          <t>kk_5051084066</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>01071157671</t>
+          <t>01032038750</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>172897</t>
+          <t>311696</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_260603_SEASONOFF</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>kk_3810304670</t>
+          <t>attack0418</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>01041348052</t>
+          <t>01094139645</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>261190</t>
+          <t>110090</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -6946,132 +6946,132 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>LMS_ECOM_200416_family</t>
+          <t>bizboard</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>kk_3372478035</t>
+          <t>cyj7088</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>01073318137</t>
+          <t>01043448832</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>240206</t>
+          <t>179751</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>seomina0907</t>
+          <t>jbin0830</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>01094631272</t>
+          <t>01025994410</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>166015</t>
+          <t>105783</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>kk_4469602027</t>
+          <t>woogi1223</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>01066870242</t>
+          <t>01044556757</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>283698</t>
+          <t>234672</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>0818_BRANDTALK_JONAS</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>kk_3519598268</t>
+          <t>rlaxotn1000</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>01039072398</t>
+          <t>01091325436</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>245899</t>
+          <t>155814</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>kk_5053805303</t>
+          <t>kk_3632939525</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>01035199923</t>
+          <t>01048431514</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>311769</t>
+          <t>248245</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -7088,71 +7088,71 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>bambae74</t>
+          <t>kk_2756203834</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>01037840714</t>
+          <t>01072683457</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>68767</t>
+          <t>208171</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>jscho01</t>
+          <t>kk_3628470198</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>01053208316</t>
+          <t>01063886569</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>139260</t>
+          <t>247993</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>kk_4323237881</t>
+          <t>kk_3800038767</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>01040657701</t>
+          <t>01045487979</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>277959</t>
+          <t>258758</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -7162,24 +7162,24 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>playalone74</t>
+          <t>kk_5055221035</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>01052891032</t>
+          <t>01090429853</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>169585</t>
+          <t>311804</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -7196,71 +7196,71 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>kk_4977819786</t>
+          <t>kk_5054440771</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>01063257991</t>
+          <t>01034218601</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>308849</t>
+          <t>311790</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>cej0422</t>
+          <t>kk_5054386338</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>01059680246</t>
+          <t>01028827342</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>308449</t>
+          <t>311788</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>kk_4824182622</t>
+          <t>kk_5053502414</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>01098590199</t>
+          <t>01062768083</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>303158</t>
+          <t>311760</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -7270,159 +7270,159 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>kk_5050508246</t>
+          <t>real3on3</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>01099167304</t>
+          <t>01052726330</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>311676</t>
+          <t>136007</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>dhk1827</t>
+          <t>wwwpsi</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>01027971827</t>
+          <t>01083430017</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>286842</t>
+          <t>215512</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>kk_2846130578</t>
+          <t>kk_3652003326</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>01064075652</t>
+          <t>01055465461</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>213236</t>
+          <t>249215</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>120253016536170385</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>kk_4279643731</t>
+          <t>jjun0297</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>01094073928</t>
+          <t>01097027205</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>275243</t>
+          <t>156884</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>6941110100332</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>kk_5029461637</t>
+          <t>hans7171</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>01037759598</t>
+          <t>01036045283</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>310962</t>
+          <t>223933</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>방문_하이브리드 오디언스</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>yan01062</t>
+          <t>nls6320</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>01076707692</t>
+          <t>01036986321</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>203357</t>
+          <t>28085</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -7432,24 +7432,24 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>방문_하이브리드 오디언스</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>kk_5048046081</t>
+          <t>kk_5051867525</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>01039004507</t>
+          <t>01075564274</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>311604</t>
+          <t>311711</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -7466,44 +7466,44 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>kk_3163403095</t>
+          <t>biueskymin</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>01094442663</t>
+          <t>01027873593</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>224415</t>
+          <t>159720</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>KAKO_CH_MESSAGE_0817_SUMMERCLEARANCE</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>kk_5054920254</t>
+          <t>sunmisopil</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>01093769998</t>
+          <t>01029605118</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>311799</t>
+          <t>132053</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -7514,1815 +7514,6 @@
       <c r="E263" t="inlineStr">
         <is>
           <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="inlineStr">
-        <is>
-          <t>kk_5055001343</t>
-        </is>
-      </c>
-      <c r="B264" t="inlineStr">
-        <is>
-          <t>01047875895</t>
-        </is>
-      </c>
-      <c r="C264" t="inlineStr">
-        <is>
-          <t>311801</t>
-        </is>
-      </c>
-      <c r="D264" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E264" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="inlineStr">
-        <is>
-          <t>kk_3685066575</t>
-        </is>
-      </c>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>01021696118</t>
-        </is>
-      </c>
-      <c r="C265" t="inlineStr">
-        <is>
-          <t>250622</t>
-        </is>
-      </c>
-      <c r="D265" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E265" t="inlineStr">
-        <is>
-          <t>naver_brandsearch_mobile</t>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="inlineStr">
-        <is>
-          <t>wasserland</t>
-        </is>
-      </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>01051765220</t>
-        </is>
-      </c>
-      <c r="C266" t="inlineStr">
-        <is>
-          <t>177860</t>
-        </is>
-      </c>
-      <c r="D266" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E266" t="inlineStr">
-        <is>
-          <t>Email_mkt</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>kk_3180692048</t>
-        </is>
-      </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>01046133289</t>
-        </is>
-      </c>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t>226239</t>
-        </is>
-      </c>
-      <c r="D267" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E267" t="inlineStr">
-        <is>
-          <t>미분류</t>
-        </is>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="inlineStr">
-        <is>
-          <t>kk_5052988564</t>
-        </is>
-      </c>
-      <c r="B268" t="inlineStr">
-        <is>
-          <t>01047680429</t>
-        </is>
-      </c>
-      <c r="C268" t="inlineStr">
-        <is>
-          <t>311734</t>
-        </is>
-      </c>
-      <c r="D268" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E268" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="inlineStr">
-        <is>
-          <t>kk_3306066072</t>
-        </is>
-      </c>
-      <c r="B269" t="inlineStr">
-        <is>
-          <t>01048303593</t>
-        </is>
-      </c>
-      <c r="C269" t="inlineStr">
-        <is>
-          <t>238116</t>
-        </is>
-      </c>
-      <c r="D269" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E269" t="inlineStr">
-        <is>
-          <t>KAKAO_alimtalk</t>
-        </is>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" t="inlineStr">
-        <is>
-          <t>kk_5049869649</t>
-        </is>
-      </c>
-      <c r="B270" t="inlineStr">
-        <is>
-          <t>01051240904</t>
-        </is>
-      </c>
-      <c r="C270" t="inlineStr">
-        <is>
-          <t>311655</t>
-        </is>
-      </c>
-      <c r="D270" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E270" t="inlineStr">
-        <is>
-          <t>naver_brandsearch_mobile</t>
-        </is>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" t="inlineStr">
-        <is>
-          <t>djae63</t>
-        </is>
-      </c>
-      <c r="B271" t="inlineStr">
-        <is>
-          <t>01027633204</t>
-        </is>
-      </c>
-      <c r="C271" t="inlineStr">
-        <is>
-          <t>245415</t>
-        </is>
-      </c>
-      <c r="D271" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E271" t="inlineStr">
-        <is>
-          <t>sa</t>
-        </is>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>kk_3864552155</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>01035193074</t>
-        </is>
-      </c>
-      <c r="C272" t="inlineStr">
-        <is>
-          <t>265863</t>
-        </is>
-      </c>
-      <c r="D272" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E272" t="inlineStr">
-        <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
-        </is>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>kk_5052479419</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>01047117155</t>
-        </is>
-      </c>
-      <c r="C273" t="inlineStr">
-        <is>
-          <t>311726</t>
-        </is>
-      </c>
-      <c r="D273" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E273" t="inlineStr">
-        <is>
-          <t>naver_brandsearch_mobile</t>
-        </is>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>hawol10041</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>01066458661</t>
-        </is>
-      </c>
-      <c r="C274" t="inlineStr">
-        <is>
-          <t>311107</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr">
-        <is>
-          <t>Official SNS</t>
-        </is>
-      </c>
-      <c r="E274" t="inlineStr">
-        <is>
-          <t>(referral)</t>
-        </is>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>kk_2867961634</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>01033939933</t>
-        </is>
-      </c>
-      <c r="C275" t="inlineStr">
-        <is>
-          <t>213870</t>
-        </is>
-      </c>
-      <c r="D275" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E275" t="inlineStr">
-        <is>
-          <t>naver_brandsearch_mobile</t>
-        </is>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>kk_5053401059</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>01021051426</t>
-        </is>
-      </c>
-      <c r="C276" t="inlineStr">
-        <is>
-          <t>311756</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E276" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>gigsfree</t>
-        </is>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>01088779997</t>
-        </is>
-      </c>
-      <c r="C277" t="inlineStr">
-        <is>
-          <t>56427</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E277" t="inlineStr">
-        <is>
-          <t>naver_brandsearch_mobile</t>
-        </is>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>kkjjg123</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>01036960451</t>
-        </is>
-      </c>
-      <c r="C278" t="inlineStr">
-        <is>
-          <t>110344</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E278" t="inlineStr">
-        <is>
-          <t>KAKAO_alimtalk</t>
-        </is>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>kk_5053312014</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>01076680710</t>
-        </is>
-      </c>
-      <c r="C279" t="inlineStr">
-        <is>
-          <t>311750</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E279" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>seep</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>01051600565</t>
-        </is>
-      </c>
-      <c r="C280" t="inlineStr">
-        <is>
-          <t>112406</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E280" t="inlineStr">
-        <is>
-          <t>naver_brandsearch_mobile</t>
-        </is>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>kk_5050922316</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>01046206459</t>
-        </is>
-      </c>
-      <c r="C281" t="inlineStr">
-        <is>
-          <t>311689</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E281" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" t="inlineStr">
-        <is>
-          <t>son2245</t>
-        </is>
-      </c>
-      <c r="B282" t="inlineStr">
-        <is>
-          <t>01039192245</t>
-        </is>
-      </c>
-      <c r="C282" t="inlineStr">
-        <is>
-          <t>164240</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E282" t="inlineStr">
-        <is>
-          <t>미분류</t>
-        </is>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" t="inlineStr">
-        <is>
-          <t>kk_5055289049</t>
-        </is>
-      </c>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>01029088281</t>
-        </is>
-      </c>
-      <c r="C283" t="inlineStr">
-        <is>
-          <t>311808</t>
-        </is>
-      </c>
-      <c r="D283" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E283" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" t="inlineStr">
-        <is>
-          <t>kk_3476177906</t>
-        </is>
-      </c>
-      <c r="B284" t="inlineStr">
-        <is>
-          <t>01079305414</t>
-        </is>
-      </c>
-      <c r="C284" t="inlineStr">
-        <is>
-          <t>244235</t>
-        </is>
-      </c>
-      <c r="D284" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E284" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" t="inlineStr">
-        <is>
-          <t>kk_5050974529</t>
-        </is>
-      </c>
-      <c r="B285" t="inlineStr">
-        <is>
-          <t>01023991588</t>
-        </is>
-      </c>
-      <c r="C285" t="inlineStr">
-        <is>
-          <t>311692</t>
-        </is>
-      </c>
-      <c r="D285" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E285" t="inlineStr">
-        <is>
-          <t>KAKO_CH_MESSAGE_0817_SUMMERCLEARANCE</t>
-        </is>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" t="inlineStr">
-        <is>
-          <t>kk_5049789835</t>
-        </is>
-      </c>
-      <c r="B286" t="inlineStr">
-        <is>
-          <t>01094739795</t>
-        </is>
-      </c>
-      <c r="C286" t="inlineStr">
-        <is>
-          <t>311653</t>
-        </is>
-      </c>
-      <c r="D286" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E286" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" t="inlineStr">
-        <is>
-          <t>kk_3723340115</t>
-        </is>
-      </c>
-      <c r="B287" t="inlineStr">
-        <is>
-          <t>01088904849</t>
-        </is>
-      </c>
-      <c r="C287" t="inlineStr">
-        <is>
-          <t>252352</t>
-        </is>
-      </c>
-      <c r="D287" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E287" t="inlineStr">
-        <is>
-          <t>KAKO_CH_MESSAGE_0817_SUMMERCLEARANCE</t>
-        </is>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" t="inlineStr">
-        <is>
-          <t>lss7705</t>
-        </is>
-      </c>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>01041147448</t>
-        </is>
-      </c>
-      <c r="C288" t="inlineStr">
-        <is>
-          <t>237569</t>
-        </is>
-      </c>
-      <c r="D288" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E288" t="inlineStr">
-        <is>
-          <t>naver_brandsearch_pc</t>
-        </is>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" t="inlineStr">
-        <is>
-          <t>kk_5050552723</t>
-        </is>
-      </c>
-      <c r="B289" t="inlineStr">
-        <is>
-          <t>01050032168</t>
-        </is>
-      </c>
-      <c r="C289" t="inlineStr">
-        <is>
-          <t>311677</t>
-        </is>
-      </c>
-      <c r="D289" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E289" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" t="inlineStr">
-        <is>
-          <t>kk_5048984503</t>
-        </is>
-      </c>
-      <c r="B290" t="inlineStr">
-        <is>
-          <t>01026775684</t>
-        </is>
-      </c>
-      <c r="C290" t="inlineStr">
-        <is>
-          <t>311630</t>
-        </is>
-      </c>
-      <c r="D290" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E290" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" t="inlineStr">
-        <is>
-          <t>kk_4319207010</t>
-        </is>
-      </c>
-      <c r="B291" t="inlineStr">
-        <is>
-          <t>01093829567</t>
-        </is>
-      </c>
-      <c r="C291" t="inlineStr">
-        <is>
-          <t>277714</t>
-        </is>
-      </c>
-      <c r="D291" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E291" t="inlineStr">
-        <is>
-          <t>KAKO_CH_MESSAGE_0817_SUMMERCLEARANCE</t>
-        </is>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" t="inlineStr">
-        <is>
-          <t>kk_5054844830</t>
-        </is>
-      </c>
-      <c r="B292" t="inlineStr">
-        <is>
-          <t>01025386330</t>
-        </is>
-      </c>
-      <c r="C292" t="inlineStr">
-        <is>
-          <t>311796</t>
-        </is>
-      </c>
-      <c r="D292" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E292" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" t="inlineStr">
-        <is>
-          <t>kk_3626416291</t>
-        </is>
-      </c>
-      <c r="B293" t="inlineStr">
-        <is>
-          <t>01049003915</t>
-        </is>
-      </c>
-      <c r="C293" t="inlineStr">
-        <is>
-          <t>247860</t>
-        </is>
-      </c>
-      <c r="D293" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E293" t="inlineStr">
-        <is>
-          <t>etc</t>
-        </is>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" t="inlineStr">
-        <is>
-          <t>minjin6789</t>
-        </is>
-      </c>
-      <c r="B294" t="inlineStr">
-        <is>
-          <t>01024062050</t>
-        </is>
-      </c>
-      <c r="C294" t="inlineStr">
-        <is>
-          <t>157791</t>
-        </is>
-      </c>
-      <c r="D294" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E294" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" t="inlineStr">
-        <is>
-          <t>kk_5053032122</t>
-        </is>
-      </c>
-      <c r="B295" t="inlineStr">
-        <is>
-          <t>01053783882</t>
-        </is>
-      </c>
-      <c r="C295" t="inlineStr">
-        <is>
-          <t>311739</t>
-        </is>
-      </c>
-      <c r="D295" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E295" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" t="inlineStr">
-        <is>
-          <t>kk_3156778149</t>
-        </is>
-      </c>
-      <c r="B296" t="inlineStr">
-        <is>
-          <t>01084700197</t>
-        </is>
-      </c>
-      <c r="C296" t="inlineStr">
-        <is>
-          <t>223775</t>
-        </is>
-      </c>
-      <c r="D296" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E296" t="inlineStr">
-        <is>
-          <t>KAKAO_alimtalk</t>
-        </is>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" t="inlineStr">
-        <is>
-          <t>kk_5053223845</t>
-        </is>
-      </c>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t>01096775572</t>
-        </is>
-      </c>
-      <c r="C297" t="inlineStr">
-        <is>
-          <t>311747</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E297" t="inlineStr">
-        <is>
-          <t>da</t>
-        </is>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" t="inlineStr">
-        <is>
-          <t>priscus</t>
-        </is>
-      </c>
-      <c r="B298" t="inlineStr">
-        <is>
-          <t>01083762352</t>
-        </is>
-      </c>
-      <c r="C298" t="inlineStr">
-        <is>
-          <t>105660</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E298" t="inlineStr">
-        <is>
-          <t>Email_mkt</t>
-        </is>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" t="inlineStr">
-        <is>
-          <t>attack0418</t>
-        </is>
-      </c>
-      <c r="B299" t="inlineStr">
-        <is>
-          <t>01094139645</t>
-        </is>
-      </c>
-      <c r="C299" t="inlineStr">
-        <is>
-          <t>110090</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E299" t="inlineStr">
-        <is>
-          <t>bizboard</t>
-        </is>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" t="inlineStr">
-        <is>
-          <t>kk_5051084066</t>
-        </is>
-      </c>
-      <c r="B300" t="inlineStr">
-        <is>
-          <t>01032038750</t>
-        </is>
-      </c>
-      <c r="C300" t="inlineStr">
-        <is>
-          <t>311696</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr">
-        <is>
-          <t>Organic Traffic</t>
-        </is>
-      </c>
-      <c r="E300" t="inlineStr">
-        <is>
-          <t>(referral)</t>
-        </is>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" t="inlineStr">
-        <is>
-          <t>jbin0830</t>
-        </is>
-      </c>
-      <c r="B301" t="inlineStr">
-        <is>
-          <t>01025994410</t>
-        </is>
-      </c>
-      <c r="C301" t="inlineStr">
-        <is>
-          <t>105783</t>
-        </is>
-      </c>
-      <c r="D301" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E301" t="inlineStr">
-        <is>
-          <t>Email_mkt</t>
-        </is>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" t="inlineStr">
-        <is>
-          <t>cyj7088</t>
-        </is>
-      </c>
-      <c r="B302" t="inlineStr">
-        <is>
-          <t>01043448832</t>
-        </is>
-      </c>
-      <c r="C302" t="inlineStr">
-        <is>
-          <t>179751</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E302" t="inlineStr">
-        <is>
-          <t>KAKAO_alimtalk</t>
-        </is>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" t="inlineStr">
-        <is>
-          <t>kk_4407853024</t>
-        </is>
-      </c>
-      <c r="B303" t="inlineStr">
-        <is>
-          <t>01052107410</t>
-        </is>
-      </c>
-      <c r="C303" t="inlineStr">
-        <is>
-          <t>281021</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E303" t="inlineStr">
-        <is>
-          <t>0818_BRANDTALK_JONAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" t="inlineStr">
-        <is>
-          <t>kk_4658095194</t>
-        </is>
-      </c>
-      <c r="B304" t="inlineStr">
-        <is>
-          <t>01099886471</t>
-        </is>
-      </c>
-      <c r="C304" t="inlineStr">
-        <is>
-          <t>293500</t>
-        </is>
-      </c>
-      <c r="D304" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E304" t="inlineStr">
-        <is>
-          <t>KAKAO_alimtalk</t>
-        </is>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" t="inlineStr">
-        <is>
-          <t>kk_3967342203</t>
-        </is>
-      </c>
-      <c r="B305" t="inlineStr">
-        <is>
-          <t>01032392912</t>
-        </is>
-      </c>
-      <c r="C305" t="inlineStr">
-        <is>
-          <t>270706</t>
-        </is>
-      </c>
-      <c r="D305" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E305" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" t="inlineStr">
-        <is>
-          <t>woogi1223</t>
-        </is>
-      </c>
-      <c r="B306" t="inlineStr">
-        <is>
-          <t>01044556757</t>
-        </is>
-      </c>
-      <c r="C306" t="inlineStr">
-        <is>
-          <t>234672</t>
-        </is>
-      </c>
-      <c r="D306" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E306" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" t="inlineStr">
-        <is>
-          <t>rlaxotn1000</t>
-        </is>
-      </c>
-      <c r="B307" t="inlineStr">
-        <is>
-          <t>01091325436</t>
-        </is>
-      </c>
-      <c r="C307" t="inlineStr">
-        <is>
-          <t>155814</t>
-        </is>
-      </c>
-      <c r="D307" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E307" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" t="inlineStr">
-        <is>
-          <t>kk_3632939525</t>
-        </is>
-      </c>
-      <c r="B308" t="inlineStr">
-        <is>
-          <t>01048431514</t>
-        </is>
-      </c>
-      <c r="C308" t="inlineStr">
-        <is>
-          <t>248245</t>
-        </is>
-      </c>
-      <c r="D308" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E308" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" t="inlineStr">
-        <is>
-          <t>kk_3628470198</t>
-        </is>
-      </c>
-      <c r="B309" t="inlineStr">
-        <is>
-          <t>01063886569</t>
-        </is>
-      </c>
-      <c r="C309" t="inlineStr">
-        <is>
-          <t>247993</t>
-        </is>
-      </c>
-      <c r="D309" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E309" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" t="inlineStr">
-        <is>
-          <t>kk_2756203834</t>
-        </is>
-      </c>
-      <c r="B310" t="inlineStr">
-        <is>
-          <t>01072683457</t>
-        </is>
-      </c>
-      <c r="C310" t="inlineStr">
-        <is>
-          <t>208171</t>
-        </is>
-      </c>
-      <c r="D310" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E310" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" t="inlineStr">
-        <is>
-          <t>kk_3800038767</t>
-        </is>
-      </c>
-      <c r="B311" t="inlineStr">
-        <is>
-          <t>01045487979</t>
-        </is>
-      </c>
-      <c r="C311" t="inlineStr">
-        <is>
-          <t>258758</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E311" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" t="inlineStr">
-        <is>
-          <t>kk_5055221035</t>
-        </is>
-      </c>
-      <c r="B312" t="inlineStr">
-        <is>
-          <t>01090429853</t>
-        </is>
-      </c>
-      <c r="C312" t="inlineStr">
-        <is>
-          <t>311804</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E312" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" t="inlineStr">
-        <is>
-          <t>kk_5054440771</t>
-        </is>
-      </c>
-      <c r="B313" t="inlineStr">
-        <is>
-          <t>01034218601</t>
-        </is>
-      </c>
-      <c r="C313" t="inlineStr">
-        <is>
-          <t>311790</t>
-        </is>
-      </c>
-      <c r="D313" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E313" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" t="inlineStr">
-        <is>
-          <t>kk_5054386338</t>
-        </is>
-      </c>
-      <c r="B314" t="inlineStr">
-        <is>
-          <t>01028827342</t>
-        </is>
-      </c>
-      <c r="C314" t="inlineStr">
-        <is>
-          <t>311788</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E314" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" t="inlineStr">
-        <is>
-          <t>kk_5053502414</t>
-        </is>
-      </c>
-      <c r="B315" t="inlineStr">
-        <is>
-          <t>01062768083</t>
-        </is>
-      </c>
-      <c r="C315" t="inlineStr">
-        <is>
-          <t>311760</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E315" t="inlineStr">
-        <is>
-          <t>naver_brandsearch_pc</t>
-        </is>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" t="inlineStr">
-        <is>
-          <t>real3on3</t>
-        </is>
-      </c>
-      <c r="B316" t="inlineStr">
-        <is>
-          <t>01052726330</t>
-        </is>
-      </c>
-      <c r="C316" t="inlineStr">
-        <is>
-          <t>136007</t>
-        </is>
-      </c>
-      <c r="D316" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E316" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" t="inlineStr">
-        <is>
-          <t>kk_3652003326</t>
-        </is>
-      </c>
-      <c r="B317" t="inlineStr">
-        <is>
-          <t>01055465461</t>
-        </is>
-      </c>
-      <c r="C317" t="inlineStr">
-        <is>
-          <t>249215</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E317" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" t="inlineStr">
-        <is>
-          <t>wwwpsi</t>
-        </is>
-      </c>
-      <c r="B318" t="inlineStr">
-        <is>
-          <t>01083430017</t>
-        </is>
-      </c>
-      <c r="C318" t="inlineStr">
-        <is>
-          <t>215512</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E318" t="inlineStr">
-        <is>
-          <t>KAKAO_alimtalk</t>
-        </is>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" t="inlineStr">
-        <is>
-          <t>kk_4664109798</t>
-        </is>
-      </c>
-      <c r="B319" t="inlineStr">
-        <is>
-          <t>01076880540</t>
-        </is>
-      </c>
-      <c r="C319" t="inlineStr">
-        <is>
-          <t>293870</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E319" t="inlineStr">
-        <is>
-          <t>KAKAO_alimtalk</t>
-        </is>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" t="inlineStr">
-        <is>
-          <t>kk_5049274215</t>
-        </is>
-      </c>
-      <c r="B320" t="inlineStr">
-        <is>
-          <t>01030583633</t>
-        </is>
-      </c>
-      <c r="C320" t="inlineStr">
-        <is>
-          <t>311635</t>
-        </is>
-      </c>
-      <c r="D320" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E320" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" t="inlineStr">
-        <is>
-          <t>jjun0297</t>
-        </is>
-      </c>
-      <c r="B321" t="inlineStr">
-        <is>
-          <t>01097027205</t>
-        </is>
-      </c>
-      <c r="C321" t="inlineStr">
-        <is>
-          <t>156884</t>
-        </is>
-      </c>
-      <c r="D321" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E321" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" t="inlineStr">
-        <is>
-          <t>hans7171</t>
-        </is>
-      </c>
-      <c r="B322" t="inlineStr">
-        <is>
-          <t>01036045283</t>
-        </is>
-      </c>
-      <c r="C322" t="inlineStr">
-        <is>
-          <t>223933</t>
-        </is>
-      </c>
-      <c r="D322" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E322" t="inlineStr">
-        <is>
-          <t>방문_하이브리드 오디언스</t>
-        </is>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" t="inlineStr">
-        <is>
-          <t>biueskymin</t>
-        </is>
-      </c>
-      <c r="B323" t="inlineStr">
-        <is>
-          <t>01027873593</t>
-        </is>
-      </c>
-      <c r="C323" t="inlineStr">
-        <is>
-          <t>159720</t>
-        </is>
-      </c>
-      <c r="D323" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E323" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" t="inlineStr">
-        <is>
-          <t>nls6320</t>
-        </is>
-      </c>
-      <c r="B324" t="inlineStr">
-        <is>
-          <t>01036986321</t>
-        </is>
-      </c>
-      <c r="C324" t="inlineStr">
-        <is>
-          <t>28085</t>
-        </is>
-      </c>
-      <c r="D324" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E324" t="inlineStr">
-        <is>
-          <t>방문_하이브리드 오디언스</t>
-        </is>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" t="inlineStr">
-        <is>
-          <t>kk_5051867525</t>
-        </is>
-      </c>
-      <c r="B325" t="inlineStr">
-        <is>
-          <t>01075564274</t>
-        </is>
-      </c>
-      <c r="C325" t="inlineStr">
-        <is>
-          <t>311711</t>
-        </is>
-      </c>
-      <c r="D325" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E325" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="326">
-      <c r="A326" t="inlineStr">
-        <is>
-          <t>sunmisopil</t>
-        </is>
-      </c>
-      <c r="B326" t="inlineStr">
-        <is>
-          <t>01029605118</t>
-        </is>
-      </c>
-      <c r="C326" t="inlineStr">
-        <is>
-          <t>132053</t>
-        </is>
-      </c>
-      <c r="D326" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E326" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" t="inlineStr">
-        <is>
-          <t>baekboss</t>
-        </is>
-      </c>
-      <c r="B327" t="inlineStr">
-        <is>
-          <t>01020458081</t>
-        </is>
-      </c>
-      <c r="C327" t="inlineStr">
-        <is>
-          <t>141316</t>
-        </is>
-      </c>
-      <c r="D327" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E327" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" t="inlineStr">
-        <is>
-          <t>kk_3835673508</t>
-        </is>
-      </c>
-      <c r="B328" t="inlineStr">
-        <is>
-          <t>01033471361</t>
-        </is>
-      </c>
-      <c r="C328" t="inlineStr">
-        <is>
-          <t>263971</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E328" t="inlineStr">
-        <is>
-          <t>naver_brandsearch_mobile</t>
-        </is>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" t="inlineStr">
-        <is>
-          <t>kk_5048712425</t>
-        </is>
-      </c>
-      <c r="B329" t="inlineStr">
-        <is>
-          <t>01090226408</t>
-        </is>
-      </c>
-      <c r="C329" t="inlineStr">
-        <is>
-          <t>311620</t>
-        </is>
-      </c>
-      <c r="D329" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E329" t="inlineStr">
-        <is>
-          <t>방문_하이브리드 오디언스</t>
-        </is>
-      </c>
-    </row>
-    <row r="330">
-      <c r="A330" t="inlineStr">
-        <is>
-          <t>ppi4346</t>
-        </is>
-      </c>
-      <c r="B330" t="inlineStr">
-        <is>
-          <t>01029718257</t>
-        </is>
-      </c>
-      <c r="C330" t="inlineStr">
-        <is>
-          <t>227795</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E330" t="inlineStr">
-        <is>
-          <t>Email_mkt</t>
         </is>
       </c>
     </row>

--- a/reports/member_funnel/downloads/member_funnel_1m_non_buyer.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1m_non_buyer.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E263"/>
+  <dimension ref="A1:E208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,44 +446,44 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>kjjopen</t>
+          <t>inhip</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>01086035744</t>
+          <t>01027705324</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>174297</t>
+          <t>167335</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>[PF]전환_카탈로그(1865,관심사_01)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>inhip</t>
+          <t>pearl52</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>01027705324</t>
+          <t>01050351018</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>167335</t>
+          <t>239776</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -493,78 +493,78 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>[PF]전환_카탈로그(1865,관심사_01)</t>
+          <t>da</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>pearl52</t>
+          <t>kk_4993751323</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>01050351018</t>
+          <t>01053138487</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>239776</t>
+          <t>309590</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>방문_하이브리드 오디언스</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>kk_4993751323</t>
+          <t>kk_4403816883</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>01053138487</t>
+          <t>01097910906</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>309590</t>
+          <t>280909</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>방문_하이브리드 오디언스</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>kk_3494319831</t>
+          <t>kk_3840423259</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>01088337167</t>
+          <t>01050355480</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>245102</t>
+          <t>264298</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -574,132 +574,132 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>kk_4403816883</t>
+          <t>passion1984</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>01097910906</t>
+          <t>01064630333</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>280909</t>
+          <t>264683</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>kk_4929043811</t>
+          <t>kk_5053218420</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>01037904341</t>
+          <t>01053426954</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>307164</t>
+          <t>311746</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>bizboard</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>kk_3840423259</t>
+          <t>skku2738</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>01050355480</t>
+          <t>01074152738</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>264298</t>
+          <t>35128</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>passion1984</t>
+          <t>gbj20022002</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>01064630333</t>
+          <t>01053509041</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>264683</t>
+          <t>53032</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>rudalsla</t>
+          <t>kk_3433423317</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>01071949782</t>
+          <t>01075326556</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>306362</t>
+          <t>242341</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -709,24 +709,24 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kk_5053218420</t>
+          <t>hjb007</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>01053426954</t>
+          <t>01096664026</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>311746</t>
+          <t>144397</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -736,51 +736,51 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>skku2738</t>
+          <t>poweryys</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>01074152738</t>
+          <t>01089678835</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>35128</t>
+          <t>214318</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>gbj20022002</t>
+          <t>kk_5034001705</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>01053509041</t>
+          <t>01090601731</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>53032</t>
+          <t>311133</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -790,24 +790,24 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>kk_3433423317</t>
+          <t>kk_5046820175</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>01075326556</t>
+          <t>01062781955</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>242341</t>
+          <t>311563</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -817,24 +817,24 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>방문_하이브리드 오디언스</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>hjb007</t>
+          <t>honor181</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>01096664026</t>
+          <t>01046301211</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>144397</t>
+          <t>192770</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -844,78 +844,78 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>poweryys</t>
+          <t>limsoo1719</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>01089678835</t>
+          <t>01055751719</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>214318</t>
+          <t>84759</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>kk_5034001705</t>
+          <t>jpm111</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>01090601731</t>
+          <t>01029304010</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>311133</t>
+          <t>249216</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>kk_5046820175</t>
+          <t>kk_4973864658</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>01062781955</t>
+          <t>01023113061</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>311563</t>
+          <t>308691</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -932,17 +932,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>kk_3407332090</t>
+          <t>kk_3184721081</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>01073480423</t>
+          <t>01085470105</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>241393</t>
+          <t>229171</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -952,24 +952,24 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_MENU_0209_NEWYEAR</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>honor181</t>
+          <t>swsun9</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>01046301211</t>
+          <t>01097889718</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>192770</t>
+          <t>295157</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -979,24 +979,24 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>limsoo1719</t>
+          <t>sky2446</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>01055751719</t>
+          <t>01086189169</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>84759</t>
+          <t>310077</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1006,51 +1006,51 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>da</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>jpm111</t>
+          <t>sooenter2021</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>01029304010</t>
+          <t>01051830725</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>249216</t>
+          <t>310304</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>kk_4973864658</t>
+          <t>kk_3775635739</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>01023113061</t>
+          <t>01047873237</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>308691</t>
+          <t>255851</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1060,24 +1060,24 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>방문_하이브리드 오디언스</t>
+          <t>[PF]A+SC_상시(1865MF,논타겟)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>kk_3184721081</t>
+          <t>kk_3147981567</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>01085470105</t>
+          <t>01072033421</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>229171</t>
+          <t>223217</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1087,78 +1087,78 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0209_NEWYEAR</t>
+          <t>KAKAO_CH_MENU_0702_REVERSEDOWN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>swsun9</t>
+          <t>kk_4209546622</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>01097889718</t>
+          <t>01079193288</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>295157</t>
+          <t>272272</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>sky2446</t>
+          <t>kk_4315111161</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>01086189169</t>
+          <t>01080806591</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>310077</t>
+          <t>277461</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>kk_3697411135</t>
+          <t>kk_4647481524</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>01074605090</t>
+          <t>01030569095</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>251206</t>
+          <t>292864</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1168,51 +1168,51 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>thebebob</t>
+          <t>hajd1011</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>01094365308</t>
+          <t>01054401373</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>196123</t>
+          <t>283249</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>sooenter2021</t>
+          <t>kk_5008721553</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>01051830725</t>
+          <t>01089905677</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>310304</t>
+          <t>310248</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1222,132 +1222,132 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>kk_3775635739</t>
+          <t>kk_4615977966</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>01047873237</t>
+          <t>01029473782</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>255851</t>
+          <t>290690</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>[PF]A+SC_상시(1865MF,논타겟)</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>kk_3147981567</t>
+          <t>kk_4516410827</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>01072033421</t>
+          <t>01048475313</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>223217</t>
+          <t>285997</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0702_REVERSEDOWN</t>
+          <t>da</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>kk_4209546622</t>
+          <t>kk_5036115734</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>01079193288</t>
+          <t>01046709214</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>272272</t>
+          <t>311217</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>kk_4315111161</t>
+          <t>kk_2751892064_2</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>01080806591</t>
+          <t>01044569101</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>277461</t>
+          <t>282142</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>[PF]전환_상시(2565MF,비구매자30일)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>jakelee</t>
+          <t>kk_5048808976</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>01027223531</t>
+          <t>01026908279</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>16193</t>
+          <t>311623</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1357,24 +1357,24 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>kk_4647481524</t>
+          <t>kk_4940334145</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>01030569095</t>
+          <t>01025490108</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>292864</t>
+          <t>307549</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1384,78 +1384,78 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>hajd1011</t>
+          <t>kk_4387186836</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>01054401373</t>
+          <t>01085670209</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>283249</t>
+          <t>280506</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>0716_SEASON_OFF_2ND</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>kk_5008721553</t>
+          <t>romanohong</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>01089905677</t>
+          <t>01089301124</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>310248</t>
+          <t>32607</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>0520</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>arrtieom</t>
+          <t>uofnywam</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>01071593949</t>
+          <t>01025062538</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>141170</t>
+          <t>204156</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1465,78 +1465,78 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0521_BAHAMA1</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>kk_4615977966</t>
+          <t>chokiwbang</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>01029473782</t>
+          <t>01052258818</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>290690</t>
+          <t>140204</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>kk_4516410827</t>
+          <t>kk_4468049816</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>01048475313</t>
+          <t>01079335600</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>285997</t>
+          <t>283582</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>KAKAO_CH_MESSAGE_0226_BTS</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>kk_5036115734</t>
+          <t>kk_5050299156</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>01046709214</t>
+          <t>01026976598</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>311217</t>
+          <t>311666</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>kk_2751892064_2</t>
+          <t>naroo27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>01044569101</t>
+          <t>01075300052</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>282142</t>
+          <t>102129</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1573,78 +1573,78 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자30일)</t>
+          <t>LMS_ECOM_0425_FAMILYSALE</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>lbw1427</t>
+          <t>kk_3179837389</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>01050283447</t>
+          <t>01089490421</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>23189</t>
+          <t>225507</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>0803_SUMMER_LAST_CHANCE</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>kk_5048808976</t>
+          <t>kk_4582648301</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>01026908279</t>
+          <t>01040451815</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>311623</t>
+          <t>288564</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>kk_4940334145</t>
+          <t>aceykh</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>01025490108</t>
+          <t>01041402352</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>307549</t>
+          <t>140002</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1654,105 +1654,105 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>EDM_TOP</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>kk_4387186836</t>
+          <t>kk_3849010182</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>01085670209</t>
+          <t>01071058942</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>280506</t>
+          <t>264944</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0716_SEASON_OFF_2ND</t>
+          <t>etc</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>romanohong</t>
+          <t>kk_4481940140</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>01089301124</t>
+          <t>01065676272</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>32607</t>
+          <t>284338</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0520</t>
+          <t>[PF_SA] 컬럼비아 상시</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>uofnywam</t>
+          <t>aaeolus</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>01025062538</t>
+          <t>01082605032</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>204156</t>
+          <t>282510</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>etc</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>kk_3216728258</t>
+          <t>kk_3769382715</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>01082974119</t>
+          <t>01098220944</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>232259</t>
+          <t>255392</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1762,159 +1762,159 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>chokiwbang</t>
+          <t>kk_3772986666</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>01052258818</t>
+          <t>01085470459</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>140204</t>
+          <t>255687</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>kk_4468049816</t>
+          <t>herowill</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>01079335600</t>
+          <t>01088996520</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>283582</t>
+          <t>85660</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0226_BTS</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>kk_5050299156</t>
+          <t>wnsvy2957</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>01026976598</t>
+          <t>01052632952</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>311666</t>
+          <t>283008</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>naroo27</t>
+          <t>kk_3182977787</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>01075300052</t>
+          <t>01085398119</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>102129</t>
+          <t>228089</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0425_FAMILYSALE</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ugjina</t>
+          <t>kk_2845811024_3</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>01065057791</t>
+          <t>01083771174</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>242092</t>
+          <t>307634</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0622</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>kk_3179837389</t>
+          <t>kk_3047832258</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>01089490421</t>
+          <t>01053403023</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>225507</t>
+          <t>220442</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1924,267 +1924,267 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0803_SUMMER_LAST_CHANCE</t>
+          <t>EDM_0329</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>kk_4582648301</t>
+          <t>kk_4319247532</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>01040451815</t>
+          <t>01088594122</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>288564</t>
+          <t>277718</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>aceykh</t>
+          <t>kk_5053571972</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>01041402352</t>
+          <t>01062303845</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>140002</t>
+          <t>311761</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>EDM_TOP</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>kk_3849010182</t>
+          <t>kk_5041074251</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>01071058942</t>
+          <t>01058983349</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>264944</t>
+          <t>311361</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>120253016536170385</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>kk_4481940140</t>
+          <t>tmdwosnsk</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>01065676272</t>
+          <t>01040847350</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>284338</t>
+          <t>239452</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>[PF_SA] 컬럼비아 상시</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>aaeolus</t>
+          <t>kk_3099382486</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>01082605032</t>
+          <t>01093078148</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>282510</t>
+          <t>221525</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>kk_3769382715</t>
+          <t>kk_5054179034</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>01098220944</t>
+          <t>01066850120</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>255392</t>
+          <t>311781</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>kk_3801004682</t>
+          <t>kk_4997974077</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>01024159216</t>
+          <t>01040095693</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>258930</t>
+          <t>309775</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>kk_3772986666</t>
+          <t>yk8809</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>01085470459</t>
+          <t>01023568809</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>255687</t>
+          <t>199548</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>herowill</t>
+          <t>dyckim</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>01088996520</t>
+          <t>01044401262</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>85660</t>
+          <t>310573</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>wnsvy2957</t>
+          <t>kk_5051879020</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>01052632952</t>
+          <t>01071731874</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>283008</t>
+          <t>311712</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2194,78 +2194,78 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>da</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>kk_3182977787</t>
+          <t>itsuky3785</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>01085398119</t>
+          <t>01033352103</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>228089</t>
+          <t>288167</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>kk_2845811024_3</t>
+          <t>khs0905</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>01083771174</t>
+          <t>01076640154</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>307634</t>
+          <t>137732</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>kk_3047832258</t>
+          <t>nada1989</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>01053403023</t>
+          <t>01089413334</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>220442</t>
+          <t>203214</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2275,78 +2275,78 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>EDM_0329</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>kk_4319247532</t>
+          <t>kk_3111973500</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>01088594122</t>
+          <t>01064187132</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>277718</t>
+          <t>267677</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>potanion</t>
+          <t>redsuede</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>01027653082</t>
+          <t>01032879838</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>215442</t>
+          <t>273348</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>kk_5053571972</t>
+          <t>kk_5052884183</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>01062303845</t>
+          <t>01030388284</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>311761</t>
+          <t>311732</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2356,24 +2356,24 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>naversa_pc</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>kk_5041074251</t>
+          <t>kk_5053135733</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>01058983349</t>
+          <t>01062083028</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>311361</t>
+          <t>311742</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2383,24 +2383,24 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>120253016536170385</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>tmdwosnsk</t>
+          <t>kk_4671019003</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>01040847350</t>
+          <t>01064700873</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>239452</t>
+          <t>294341</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2417,71 +2417,71 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>kk_3099382486</t>
+          <t>kk_5049890573</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>01093078148</t>
+          <t>01094328346</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>221525</t>
+          <t>311657</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>kk_5054179034</t>
+          <t>kk_5051471907</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>01066850120</t>
+          <t>01092552888</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>311781</t>
+          <t>311705</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>kk_4997974077</t>
+          <t>kk_5053813602</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>01040095693</t>
+          <t>01094931734</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>309775</t>
+          <t>311771</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2491,105 +2491,105 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>etc</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>yk8809</t>
+          <t>kk_5052996890</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>01023568809</t>
+          <t>01028467527</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>199548</t>
+          <t>311736</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>etc</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>leek78910</t>
+          <t>kk_4830179048</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>01054949937</t>
+          <t>01059171953</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>211793</t>
+          <t>303507</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>0610</t>
+          <t>naversa_mo</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>dyckim</t>
+          <t>hhgg6482</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>01044401262</t>
+          <t>01052195642</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>310573</t>
+          <t>290916</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>kk_5051879020</t>
+          <t>sclpion</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>01071731874</t>
+          <t>01088740653</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>311712</t>
+          <t>141669</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2599,24 +2599,24 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>itsuky3785</t>
+          <t>gogo4135</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>01033352103</t>
+          <t>01088831877</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>288167</t>
+          <t>170683</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2633,157 +2633,157 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>khs0905</t>
+          <t>fcozy</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>01076640154</t>
+          <t>01083998861</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>137732</t>
+          <t>114021</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>nada1989</t>
+          <t>kk_5052989693</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>01089413334</t>
+          <t>01095421888</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>203214</t>
+          <t>311735</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>etc</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>kys6181</t>
+          <t>lees0925</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>01065450817</t>
+          <t>01089944951</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>196299</t>
+          <t>284991</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>kk_4303259863</t>
+          <t>kk_5053146625</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>01088772815</t>
+          <t>01092265566</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>276683</t>
+          <t>311743</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>etc</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>kk_5010416607</t>
+          <t>kk_5040443935</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>01089512927</t>
+          <t>01086507863</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>310314</t>
+          <t>311339</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>[PF]전환_상시(2565MF,비구매자30일)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>kk_3111973500</t>
+          <t>kk_5050610678</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>01064187132</t>
+          <t>01093820086</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>267677</t>
+          <t>311678</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -2795,44 +2795,44 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>redsuede</t>
+          <t>russia55</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>01032879838</t>
+          <t>01022813614</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>273348</t>
+          <t>170004</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>kk_5052884183</t>
+          <t>molgue</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>01030388284</t>
+          <t>01096385787</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>311732</t>
+          <t>189580</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2842,105 +2842,105 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>naversa_pc</t>
+          <t>방문_하이브리드 오디언스</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>kk_5053135733</t>
+          <t>kk_4234730563</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>01062083028</t>
+          <t>01072748373</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>311742</t>
+          <t>273531</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>kk_4671019003</t>
+          <t>piung8</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>01064700873</t>
+          <t>01024302128</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>294341</t>
+          <t>241561</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>da</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>kk_5049890573</t>
+          <t>kk_5053573200</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>01094328346</t>
+          <t>01050217981</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>311657</t>
+          <t>311762</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>kk_5051471907</t>
+          <t>kk_2794341634</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>01092552888</t>
+          <t>01062258622</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>311705</t>
+          <t>210525</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2950,51 +2950,51 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>kk_5053813602</t>
+          <t>humi312</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>01094931734</t>
+          <t>01032018321</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>311771</t>
+          <t>109372</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>방문_하이브리드 오디언스</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>h11145</t>
+          <t>kk_3392066640</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>01073342519</t>
+          <t>01065021283</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>311682</t>
+          <t>240983</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3004,78 +3004,78 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>방문_하이브리드 오디언스</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>kk_5052996890</t>
+          <t>kk_3140884947</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>01028467527</t>
+          <t>01081538888</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>311736</t>
+          <t>222841</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>0818_BRANDTALK_JONAS</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>kk_4830179048</t>
+          <t>kk_4445795434</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>01059171953</t>
+          <t>01027315428</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>303507</t>
+          <t>282265</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>0803_Clearance</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>bubbo7942</t>
+          <t>mupasa1010</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>01041446001</t>
+          <t>01098195600</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>311654</t>
+          <t>197579</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3085,105 +3085,105 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>방문_하이브리드 오디언스</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>hhgg6482</t>
+          <t>kk_4967367828</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>01052195642</t>
+          <t>01090955298</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>290916</t>
+          <t>308392</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>sclpion</t>
+          <t>icoram</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>01088740653</t>
+          <t>01091898092</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>141669</t>
+          <t>311807</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>gogo4135</t>
+          <t>kk_3222864535</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>01088831877</t>
+          <t>01087438761</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>170683</t>
+          <t>232810</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>fcozy</t>
+          <t>della96</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>01083998861</t>
+          <t>01071782565</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>114021</t>
+          <t>119198</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3193,186 +3193,186 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>방문_하이브리드 오디언스</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>kk_5052989693</t>
+          <t>kk_5052196631</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>01095421888</t>
+          <t>01035951351</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>311735</t>
+          <t>311723</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>lees0925</t>
+          <t>kk_4915210068</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>01089944951</t>
+          <t>01054111693</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>284991</t>
+          <t>306647</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>kk_5053146625</t>
+          <t>kk_4286220576</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>01092265566</t>
+          <t>01053587782</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>311743</t>
+          <t>275624</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>LMS_ECOM_200416_seasonoff</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>kk_5040443935</t>
+          <t>kk_2919185721</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>01086507863</t>
+          <t>01034872320</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>311339</t>
+          <t>215776</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자30일)</t>
+          <t>etc</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>he2008417</t>
+          <t>kk_4213116180</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>01091680417</t>
+          <t>01094956022</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>153431</t>
+          <t>272450</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKO_CH_MESSAGE_0817_SUMMERCLEARANCE</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>kk_5050610678</t>
+          <t>ghffhs</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>01093820086</t>
+          <t>01086461880</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>311678</t>
+          <t>172816</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>yuna8819</t>
+          <t>hiyeom</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>01027098819</t>
+          <t>01092193123</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>278063</t>
+          <t>73820</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3382,159 +3382,159 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>0705_SEASON_OFF_2ND</t>
+          <t>da</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>kk_5049571823</t>
+          <t>kk_3211764926</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>01063482295</t>
+          <t>01065592320</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>311646</t>
+          <t>231794</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>방문_하이브리드 오디언스</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>russia55</t>
+          <t>jsy90</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>01022813614</t>
+          <t>01055153689</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>170004</t>
+          <t>304378</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0410pants2</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>molgue</t>
+          <t>kk_3923084698</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>01096385787</t>
+          <t>01093992638</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>189580</t>
+          <t>268693</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>방문_하이브리드 오디언스</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>kk_4234730563</t>
+          <t>kk_4902163917</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>01072748373</t>
+          <t>01091388108</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>273531</t>
+          <t>306260</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>piung8</t>
+          <t>kk_5054290902</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>01024302128</t>
+          <t>01089708874</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>241561</t>
+          <t>311785</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>kk_5053573200</t>
+          <t>kkk570908</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>01050217981</t>
+          <t>01037997125</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>311762</t>
+          <t>268558</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -3544,24 +3544,24 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>da</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>kk_2794341634</t>
+          <t>kk_3415923718</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>01062258622</t>
+          <t>01087476815</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>210525</t>
+          <t>241616</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -3571,105 +3571,105 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>da</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>humi312</t>
+          <t>younge789</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>01032018321</t>
+          <t>01085185168</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>109372</t>
+          <t>169078</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>방문_하이브리드 오디언스</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>kk_3392066640</t>
+          <t>kk_5054464771</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>01065021283</t>
+          <t>01087583944</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>240983</t>
+          <t>311791</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>kk_3140884947</t>
+          <t>kk_3157182568</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>01081538888</t>
+          <t>01057620105</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>222841</t>
+          <t>223820</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>0818_BRANDTALK_JONAS</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>kk_4445795434</t>
+          <t>happyglory81</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>01027315428</t>
+          <t>01064760332</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>282265</t>
+          <t>135652</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -3679,24 +3679,24 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>0803_Clearance</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>mupasa1010</t>
+          <t>kk_5052645690</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>01098195600</t>
+          <t>01094486334</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>197579</t>
+          <t>311729</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -3706,51 +3706,51 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>drunkenly</t>
+          <t>kk_5054057588</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>01047087372</t>
+          <t>01047332261</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>182608</t>
+          <t>311778</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>kk_4967367828</t>
+          <t>kk_4288755561</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>01090955298</t>
+          <t>01042420896</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>308392</t>
+          <t>275791</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -3760,24 +3760,24 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKO_CH_MESSAGE_0817_TRAILRUN</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>icoram</t>
+          <t>kk_3303914582</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>01091898092</t>
+          <t>01028715525</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>311807</t>
+          <t>237924</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -3794,233 +3794,233 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>kk_3222864535</t>
+          <t>kk_5050311909</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>01087438761</t>
+          <t>01039067015</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>232810</t>
+          <t>311667</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_MENU_0728_AMBASSADOR</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>della96</t>
+          <t>daekwangsu</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>01071782565</t>
+          <t>01055970579</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>119198</t>
+          <t>96203</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>방문_하이브리드 오디언스</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>kk_5052196631</t>
+          <t>kk_3622891451</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>01035951351</t>
+          <t>01053726280</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>311723</t>
+          <t>247735</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>kk_4915210068</t>
+          <t>kk_3842461525</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>01054111693</t>
+          <t>01077300704</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>306647</t>
+          <t>264453</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>0520</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>kk_4286220576</t>
+          <t>merhen</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>01053587782</t>
+          <t>01025129134</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>275624</t>
+          <t>89491</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>LMS_ECOM_200416_seasonoff</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>kk_2919185721</t>
+          <t>kk_3728610953</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>01034872320</t>
+          <t>01092914950</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>215776</t>
+          <t>252762</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>kk_4213116180</t>
+          <t>gusrb5315</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>01094956022</t>
+          <t>01033445315</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>272450</t>
+          <t>240662</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>KAKO_CH_MESSAGE_0817_SUMMERCLEARANCE</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ghffhs</t>
+          <t>kk_5053760478</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>01086461880</t>
+          <t>01025944738</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>172816</t>
+          <t>311768</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>hiyeom</t>
+          <t>ic8871</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>01092193123</t>
+          <t>01063456741</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>73820</t>
+          <t>117110</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -4030,51 +4030,51 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>kk_3211764926</t>
+          <t>sm297</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>01065592320</t>
+          <t>01089954070</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>231794</t>
+          <t>172466</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>etc</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>jsy90</t>
+          <t>sunam12</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>01055153689</t>
+          <t>01081404180</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>304378</t>
+          <t>148548</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -4084,159 +4084,159 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410pants2</t>
+          <t>KAKAO_CH_MESSAGE_260702_SEASONOFF2ND</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>kk_3923084698</t>
+          <t>soleado</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>01093992638</t>
+          <t>01067078981</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>268693</t>
+          <t>289679</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>kk_4902163917</t>
+          <t>kk_3035383266</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>01091388108</t>
+          <t>01036728869</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>306260</t>
+          <t>219867</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>kk_5050813376</t>
+          <t>wjddmsp4</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>01032764500</t>
+          <t>01027170361</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>311685</t>
+          <t>103841</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>kk_5054290902</t>
+          <t>kk_4442668340</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>01089708874</t>
+          <t>01089979956</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>311785</t>
+          <t>282163</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>etc</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>kk_5049435171</t>
+          <t>kk_4679174258</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>01082504237</t>
+          <t>01054503197</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>311643</t>
+          <t>294810</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>kkk570908</t>
+          <t>kk_5053440830</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>01037997125</t>
+          <t>01075725067</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>268558</t>
+          <t>311758</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -4246,186 +4246,186 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>방문_하이브리드 오디언스</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>kk_3415923718</t>
+          <t>kk_5026095899</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>01087476815</t>
+          <t>01086935544</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>241616</t>
+          <t>310852</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>younghee1c</t>
+          <t>mgoon1005</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>01045678561</t>
+          <t>01054720108</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>174797</t>
+          <t>266467</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>KAKO_CH_MESSAGE_0817_SUMMERCLEARANCE</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>kk_4667580040</t>
+          <t>kk_3666720704</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>01097556194</t>
+          <t>01033458251</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>294108</t>
+          <t>249880</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>KAKAO_CH_MESSAGE_260702_WATERPROOFITEM</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>younge789</t>
+          <t>kk_3733604305</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>01085185168</t>
+          <t>01046180063</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>169078</t>
+          <t>253138</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_MESSAGE_0730_OMNISHADE</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>kk_5054464771</t>
+          <t>dbeodus12</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>01087583944</t>
+          <t>01094952956</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>311791</t>
+          <t>177779</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>kk_3157182568</t>
+          <t>kk_5025530724</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>01057620105</t>
+          <t>01055050266</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>223820</t>
+          <t>310814</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>happyglory81</t>
+          <t>kk_4442439433</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>01064760332</t>
+          <t>01075664837</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>135652</t>
+          <t>282157</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -4435,213 +4435,213 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>0520</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>kk_5052645690</t>
+          <t>bluesung226</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>01094486334</t>
+          <t>01024421910</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>311729</t>
+          <t>205476</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>kk_5054057588</t>
+          <t>kk_3168093587</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>01047332261</t>
+          <t>01087964559</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>311778</t>
+          <t>224737</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>kk_4288755561</t>
+          <t>kk_5054226033</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>01042420896</t>
+          <t>01084058475</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>275791</t>
+          <t>311784</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>KAKO_CH_MESSAGE_0817_TRAILRUN</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>kk_3170595620</t>
+          <t>kk_5052086920</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>01027919785</t>
+          <t>01087726668</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>224951</t>
+          <t>311718</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>etc</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>kk_3303914582</t>
+          <t>june715</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>01028715525</t>
+          <t>01071157671</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>237924</t>
+          <t>172897</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_MENU_260603_SEASONOFF</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>kk_5050311909</t>
+          <t>kk_3372478035</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>01039067015</t>
+          <t>01073318137</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>311667</t>
+          <t>240206</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0728_AMBASSADOR</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>kk_5046654259</t>
+          <t>seomina0907</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>01054946646</t>
+          <t>01094631272</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>311556</t>
+          <t>166015</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>daekwangsu</t>
+          <t>kk_5053805303</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>01055970579</t>
+          <t>01035199923</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>96203</t>
+          <t>311769</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -4658,17 +4658,17 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>kk_3622891451</t>
+          <t>bambae74</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>01053726280</t>
+          <t>01037840714</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>247735</t>
+          <t>68767</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -4678,24 +4678,24 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>da</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>kk_3842461525</t>
+          <t>jscho01</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>01077300704</t>
+          <t>01053208316</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>264453</t>
+          <t>139260</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -4705,105 +4705,105 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>0520</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>merhen</t>
+          <t>kk_4977819786</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>01025129134</t>
+          <t>01063257991</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>89491</t>
+          <t>308849</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>kk_3728610953</t>
+          <t>kk_5050508246</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>01092914950</t>
+          <t>01099167304</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>252762</t>
+          <t>311676</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>gusrb5315</t>
+          <t>dhk1827</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>01033445315</t>
+          <t>01027971827</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>240662</t>
+          <t>286842</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>kk_5053760478</t>
+          <t>kk_2846130578</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>01025944738</t>
+          <t>01064075652</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>311768</t>
+          <t>213236</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -4813,78 +4813,78 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>120253016536170385</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ic8871</t>
+          <t>kk_5029461637</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>01063456741</t>
+          <t>01037759598</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>117110</t>
+          <t>310962</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>kk_3700715231</t>
+          <t>yan01062</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>01033535653</t>
+          <t>01076707692</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>251354</t>
+          <t>203357</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>sm297</t>
+          <t>kk_3163403095</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>01089954070</t>
+          <t>01094442663</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>172466</t>
+          <t>224415</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -4894,186 +4894,186 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>KAKO_CH_MESSAGE_0817_SUMMERCLEARANCE</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>sunam12</t>
+          <t>kk_5054920254</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>01081404180</t>
+          <t>01093769998</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>148548</t>
+          <t>311799</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_260702_SEASONOFF2ND</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>soleado</t>
+          <t>kk_5055001343</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>01067078981</t>
+          <t>01047875895</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>289679</t>
+          <t>311801</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>kk_3035383266</t>
+          <t>kk_3685066575</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>01036728869</t>
+          <t>01021696118</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>219867</t>
+          <t>250622</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>wjddmsp4</t>
+          <t>wasserland</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>01027170361</t>
+          <t>01051765220</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>103841</t>
+          <t>177860</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>kk_5001853528</t>
+          <t>kk_3180692048</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>01063062373</t>
+          <t>01046133289</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>309969</t>
+          <t>226239</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>[PF]A+SC_상시(논타겟)</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>kk_4442668340</t>
+          <t>kk_5052988564</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>01089979956</t>
+          <t>01047680429</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>282163</t>
+          <t>311734</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>fjqm1717</t>
+          <t>djae63</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>01093376905</t>
+          <t>01027633204</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>185768</t>
+          <t>245415</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -5083,24 +5083,24 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>kk_4679174258</t>
+          <t>kk_3864552155</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>01054503197</t>
+          <t>01035193074</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>294810</t>
+          <t>265863</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -5110,24 +5110,24 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>kk_5053440830</t>
+          <t>kk_5052479419</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>01075725067</t>
+          <t>01047117155</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>311758</t>
+          <t>311726</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -5137,78 +5137,78 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>방문_하이브리드 오디언스</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>kk_5026095899</t>
+          <t>kk_2867961634</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>01086935544</t>
+          <t>01033939933</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>310852</t>
+          <t>213870</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>mgoon1005</t>
+          <t>kk_5053401059</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>01054720108</t>
+          <t>01021051426</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>266467</t>
+          <t>311756</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>kk_3666720704</t>
+          <t>kkjjg123</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>01033458251</t>
+          <t>01036960451</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>249880</t>
+          <t>110344</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -5218,132 +5218,132 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_260702_WATERPROOFITEM</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>apple9420</t>
+          <t>seep</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>01062379420</t>
+          <t>01051600565</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>256551</t>
+          <t>112406</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>0803_Clearance</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>kk_3733604305</t>
+          <t>kk_5053312014</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>01046180063</t>
+          <t>01076680710</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>253138</t>
+          <t>311750</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0730_OMNISHADE</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>dbeodus12</t>
+          <t>son2245</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>01094952956</t>
+          <t>01039192245</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>177779</t>
+          <t>164240</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>kk_5025530724</t>
+          <t>kk_5055289049</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>01055050266</t>
+          <t>01029088281</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>310814</t>
+          <t>311808</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>kk_4442439433</t>
+          <t>kk_5050974529</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>01075664837</t>
+          <t>01023991588</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>282157</t>
+          <t>311692</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -5353,105 +5353,105 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>0520</t>
+          <t>KAKO_CH_MESSAGE_0817_SUMMERCLEARANCE</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>bluesung226</t>
+          <t>kk_3476177906</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>01024421910</t>
+          <t>01079305414</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>205476</t>
+          <t>244235</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>kk_5001280835</t>
+          <t>minjin6789</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>01088193949</t>
+          <t>01024062050</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>309942</t>
+          <t>157791</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>kk_3168093587</t>
+          <t>kk_5054844830</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>01087964559</t>
+          <t>01025386330</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>224737</t>
+          <t>311796</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>kk_5054226033</t>
+          <t>kk_3626416291</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>01084058475</t>
+          <t>01049003915</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>311784</t>
+          <t>247860</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -5461,24 +5461,24 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>etc</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>june715</t>
+          <t>kk_3156778149</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>01071157671</t>
+          <t>01084700197</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>172897</t>
+          <t>223775</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -5488,348 +5488,348 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_260603_SEASONOFF</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>kk_5052086920</t>
+          <t>kk_5053032122</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>01087726668</t>
+          <t>01053783882</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>311718</t>
+          <t>311739</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>kk_3810304670</t>
+          <t>kk_5053223845</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>01041348052</t>
+          <t>01096775572</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>261190</t>
+          <t>311747</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>LMS_ECOM_200416_family</t>
+          <t>da</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>kk_3372478035</t>
+          <t>kk_5051084066</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>01073318137</t>
+          <t>01032038750</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>240206</t>
+          <t>311696</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>seomina0907</t>
+          <t>attack0418</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>01094631272</t>
+          <t>01094139645</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>166015</t>
+          <t>110090</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>bizboard</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>kk_5053805303</t>
+          <t>priscus</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>01035199923</t>
+          <t>01083762352</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>311769</t>
+          <t>105660</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>bambae74</t>
+          <t>woogi1223</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>01037840714</t>
+          <t>01044556757</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>68767</t>
+          <t>234672</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>jscho01</t>
+          <t>rlaxotn1000</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>01053208316</t>
+          <t>01091325436</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>139260</t>
+          <t>155814</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>playalone74</t>
+          <t>kk_2756203834</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>01052891032</t>
+          <t>01072683457</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>169585</t>
+          <t>208171</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>kk_4977819786</t>
+          <t>kk_3628470198</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>01063257991</t>
+          <t>01063886569</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>308849</t>
+          <t>247993</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>cej0422</t>
+          <t>kk_5055221035</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>01059680246</t>
+          <t>01090429853</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>308449</t>
+          <t>311804</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>kk_4824182622</t>
+          <t>kk_5054386338</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>01098590199</t>
+          <t>01028827342</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>303158</t>
+          <t>311788</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>kk_5050508246</t>
+          <t>kk_3800038767</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>01099167304</t>
+          <t>01045487979</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>311676</t>
+          <t>258758</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>dhk1827</t>
+          <t>kk_5054440771</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>01027971827</t>
+          <t>01034218601</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>286842</t>
+          <t>311790</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -5846,17 +5846,17 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>kk_2846130578</t>
+          <t>kk_5053502414</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>01064075652</t>
+          <t>01062768083</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>213236</t>
+          <t>311760</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -5866,78 +5866,78 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>120253016536170385</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>kk_4279643731</t>
+          <t>real3on3</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>01094073928</t>
+          <t>01052726330</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>275243</t>
+          <t>136007</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>6941110100332</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>kk_5029461637</t>
+          <t>jjun0297</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>01037759598</t>
+          <t>01097027205</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>310962</t>
+          <t>156884</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>yan01062</t>
+          <t>hans7171</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>01076707692</t>
+          <t>01036045283</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>203357</t>
+          <t>223933</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -5947,78 +5947,78 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>방문_하이브리드 오디언스</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>kk_3163403095</t>
+          <t>kk_5051867525</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>01094442663</t>
+          <t>01075564274</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>224415</t>
+          <t>311711</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>KAKO_CH_MESSAGE_0817_SUMMERCLEARANCE</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>kk_5054920254</t>
+          <t>nls6320</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>01093769998</t>
+          <t>01036986321</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>311799</t>
+          <t>28085</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>방문_하이브리드 오디언스</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>kk_5055001343</t>
+          <t>biueskymin</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>01047875895</t>
+          <t>01027873593</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>311801</t>
+          <t>159720</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -6027,1491 +6027,6 @@
         </is>
       </c>
       <c r="E208" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>kk_3685066575</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>01021696118</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>250622</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>naver_brandsearch_mobile</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>wasserland</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>01051765220</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>177860</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t>Email_mkt</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>kk_3180692048</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>01046133289</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>226239</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E211" t="inlineStr">
-        <is>
-          <t>미분류</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>kk_5052988564</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>01047680429</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>311734</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E212" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>kk_3306066072</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>01048303593</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>238116</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>KAKAO_alimtalk</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>kk_5049869649</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>01051240904</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>311655</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>naver_brandsearch_mobile</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>djae63</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>01027633204</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>245415</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t>sa</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>kk_3864552155</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>01035193074</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>265863</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>kk_5052479419</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>01047117155</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>311726</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E217" t="inlineStr">
-        <is>
-          <t>naver_brandsearch_mobile</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>hawol10041</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>01066458661</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>311107</t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr">
-        <is>
-          <t>Official SNS</t>
-        </is>
-      </c>
-      <c r="E218" t="inlineStr">
-        <is>
-          <t>(referral)</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>kk_2867961634</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>01033939933</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>213870</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t>naver_brandsearch_mobile</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>kk_5053401059</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>01021051426</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>311756</t>
-        </is>
-      </c>
-      <c r="D220" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>gigsfree</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>01088779997</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>56427</t>
-        </is>
-      </c>
-      <c r="D221" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E221" t="inlineStr">
-        <is>
-          <t>naver_brandsearch_mobile</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>kkjjg123</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>01036960451</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>110344</t>
-        </is>
-      </c>
-      <c r="D222" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E222" t="inlineStr">
-        <is>
-          <t>KAKAO_alimtalk</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>kk_5053312014</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>01076680710</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>311750</t>
-        </is>
-      </c>
-      <c r="D223" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E223" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>seep</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>01051600565</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>112406</t>
-        </is>
-      </c>
-      <c r="D224" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E224" t="inlineStr">
-        <is>
-          <t>naver_brandsearch_mobile</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>kk_5050922316</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>01046206459</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>311689</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E225" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>son2245</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>01039192245</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>164240</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E226" t="inlineStr">
-        <is>
-          <t>미분류</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>kk_5055289049</t>
-        </is>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>01029088281</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>311808</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E227" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>kk_5050974529</t>
-        </is>
-      </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>01023991588</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>311692</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E228" t="inlineStr">
-        <is>
-          <t>KAKO_CH_MESSAGE_0817_SUMMERCLEARANCE</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>kk_3476177906</t>
-        </is>
-      </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>01079305414</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>244235</t>
-        </is>
-      </c>
-      <c r="D229" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E229" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>kk_3723340115</t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>01088904849</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>252352</t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E230" t="inlineStr">
-        <is>
-          <t>KAKO_CH_MESSAGE_0817_SUMMERCLEARANCE</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>kk_5049789835</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>01094739795</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>311653</t>
-        </is>
-      </c>
-      <c r="D231" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E231" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>lss7705</t>
-        </is>
-      </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>01041147448</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>237569</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E232" t="inlineStr">
-        <is>
-          <t>naver_brandsearch_pc</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>kk_5050552723</t>
-        </is>
-      </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>01050032168</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>311677</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E233" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>minjin6789</t>
-        </is>
-      </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>01024062050</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>157791</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E234" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>kk_3626416291</t>
-        </is>
-      </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>01049003915</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>247860</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E235" t="inlineStr">
-        <is>
-          <t>etc</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>kk_5054844830</t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>01025386330</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>311796</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E236" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>kk_5053032122</t>
-        </is>
-      </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>01053783882</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>311739</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E237" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>kk_5053223845</t>
-        </is>
-      </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>01096775572</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>311747</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E238" t="inlineStr">
-        <is>
-          <t>da</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>kk_3156778149</t>
-        </is>
-      </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>01084700197</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>223775</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E239" t="inlineStr">
-        <is>
-          <t>KAKAO_alimtalk</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>priscus</t>
-        </is>
-      </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>01083762352</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>105660</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E240" t="inlineStr">
-        <is>
-          <t>Email_mkt</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>kk_5051084066</t>
-        </is>
-      </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>01032038750</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>311696</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>Organic Traffic</t>
-        </is>
-      </c>
-      <c r="E241" t="inlineStr">
-        <is>
-          <t>(referral)</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>attack0418</t>
-        </is>
-      </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>01094139645</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>110090</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E242" t="inlineStr">
-        <is>
-          <t>bizboard</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>cyj7088</t>
-        </is>
-      </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>01043448832</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>179751</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E243" t="inlineStr">
-        <is>
-          <t>KAKAO_alimtalk</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="inlineStr">
-        <is>
-          <t>jbin0830</t>
-        </is>
-      </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>01025994410</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>105783</t>
-        </is>
-      </c>
-      <c r="D244" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E244" t="inlineStr">
-        <is>
-          <t>Email_mkt</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="inlineStr">
-        <is>
-          <t>woogi1223</t>
-        </is>
-      </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>01044556757</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>234672</t>
-        </is>
-      </c>
-      <c r="D245" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E245" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="inlineStr">
-        <is>
-          <t>rlaxotn1000</t>
-        </is>
-      </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>01091325436</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>155814</t>
-        </is>
-      </c>
-      <c r="D246" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E246" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>kk_3632939525</t>
-        </is>
-      </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>01048431514</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr">
-        <is>
-          <t>248245</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E247" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>kk_2756203834</t>
-        </is>
-      </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>01072683457</t>
-        </is>
-      </c>
-      <c r="C248" t="inlineStr">
-        <is>
-          <t>208171</t>
-        </is>
-      </c>
-      <c r="D248" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E248" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>kk_3628470198</t>
-        </is>
-      </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>01063886569</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>247993</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E249" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>kk_3800038767</t>
-        </is>
-      </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>01045487979</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>258758</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E250" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>kk_5055221035</t>
-        </is>
-      </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>01090429853</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>311804</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E251" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>kk_5054440771</t>
-        </is>
-      </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>01034218601</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>311790</t>
-        </is>
-      </c>
-      <c r="D252" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E252" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>kk_5054386338</t>
-        </is>
-      </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>01028827342</t>
-        </is>
-      </c>
-      <c r="C253" t="inlineStr">
-        <is>
-          <t>311788</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E253" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>kk_5053502414</t>
-        </is>
-      </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>01062768083</t>
-        </is>
-      </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>311760</t>
-        </is>
-      </c>
-      <c r="D254" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E254" t="inlineStr">
-        <is>
-          <t>naver_brandsearch_pc</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>real3on3</t>
-        </is>
-      </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>01052726330</t>
-        </is>
-      </c>
-      <c r="C255" t="inlineStr">
-        <is>
-          <t>136007</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E255" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="inlineStr">
-        <is>
-          <t>wwwpsi</t>
-        </is>
-      </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>01083430017</t>
-        </is>
-      </c>
-      <c r="C256" t="inlineStr">
-        <is>
-          <t>215512</t>
-        </is>
-      </c>
-      <c r="D256" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E256" t="inlineStr">
-        <is>
-          <t>KAKAO_alimtalk</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="inlineStr">
-        <is>
-          <t>kk_3652003326</t>
-        </is>
-      </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>01055465461</t>
-        </is>
-      </c>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t>249215</t>
-        </is>
-      </c>
-      <c r="D257" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E257" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
-        <is>
-          <t>jjun0297</t>
-        </is>
-      </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>01097027205</t>
-        </is>
-      </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>156884</t>
-        </is>
-      </c>
-      <c r="D258" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E258" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="inlineStr">
-        <is>
-          <t>hans7171</t>
-        </is>
-      </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>01036045283</t>
-        </is>
-      </c>
-      <c r="C259" t="inlineStr">
-        <is>
-          <t>223933</t>
-        </is>
-      </c>
-      <c r="D259" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E259" t="inlineStr">
-        <is>
-          <t>방문_하이브리드 오디언스</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>nls6320</t>
-        </is>
-      </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>01036986321</t>
-        </is>
-      </c>
-      <c r="C260" t="inlineStr">
-        <is>
-          <t>28085</t>
-        </is>
-      </c>
-      <c r="D260" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E260" t="inlineStr">
-        <is>
-          <t>방문_하이브리드 오디언스</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>kk_5051867525</t>
-        </is>
-      </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>01075564274</t>
-        </is>
-      </c>
-      <c r="C261" t="inlineStr">
-        <is>
-          <t>311711</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E261" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t>biueskymin</t>
-        </is>
-      </c>
-      <c r="B262" t="inlineStr">
-        <is>
-          <t>01027873593</t>
-        </is>
-      </c>
-      <c r="C262" t="inlineStr">
-        <is>
-          <t>159720</t>
-        </is>
-      </c>
-      <c r="D262" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E262" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>sunmisopil</t>
-        </is>
-      </c>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>01029605118</t>
-        </is>
-      </c>
-      <c r="C263" t="inlineStr">
-        <is>
-          <t>132053</t>
-        </is>
-      </c>
-      <c r="D263" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E263" t="inlineStr">
         <is>
           <t>Direct</t>
         </is>

--- a/reports/member_funnel/downloads/member_funnel_1m_non_buyer.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1m_non_buyer.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E208"/>
+  <dimension ref="A1:E144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -581,44 +581,44 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>passion1984</t>
+          <t>kk_5053218420</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>01064630333</t>
+          <t>01053426954</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>264683</t>
+          <t>311746</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>kk_5053218420</t>
+          <t>gbj20022002</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>01053426954</t>
+          <t>01053509041</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>311746</t>
+          <t>53032</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -628,51 +628,51 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>skku2738</t>
+          <t>kk_3433423317</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>01074152738</t>
+          <t>01075326556</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>35128</t>
+          <t>242341</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>gbj20022002</t>
+          <t>hjb007</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>01053509041</t>
+          <t>01096664026</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>53032</t>
+          <t>144397</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -682,51 +682,51 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>kk_3433423317</t>
+          <t>poweryys</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>01075326556</t>
+          <t>01089678835</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>242341</t>
+          <t>214318</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>hjb007</t>
+          <t>kk_5034001705</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>01096664026</t>
+          <t>01090601731</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>144397</t>
+          <t>311133</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -736,51 +736,51 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>poweryys</t>
+          <t>kk_5046820175</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>01089678835</t>
+          <t>01062781955</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>214318</t>
+          <t>311563</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>방문_하이브리드 오디언스</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kk_5034001705</t>
+          <t>honor181</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>01090601731</t>
+          <t>01046301211</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>311133</t>
+          <t>192770</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -790,105 +790,105 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>kk_5046820175</t>
+          <t>jpm111</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>01062781955</t>
+          <t>01029304010</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>311563</t>
+          <t>249216</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>방문_하이브리드 오디언스</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>honor181</t>
+          <t>kk_3147981567</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>01046301211</t>
+          <t>01072033421</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>192770</t>
+          <t>223217</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>KAKAO_CH_MENU_0702_REVERSEDOWN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>limsoo1719</t>
+          <t>kk_4209546622</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>01055751719</t>
+          <t>01079193288</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>84759</t>
+          <t>272272</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>jpm111</t>
+          <t>kk_4315111161</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>01029304010</t>
+          <t>01080806591</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>249216</t>
+          <t>277461</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -898,24 +898,24 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>kk_4973864658</t>
+          <t>kk_5008721553</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>01023113061</t>
+          <t>01089905677</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>308691</t>
+          <t>310248</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -925,51 +925,51 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>방문_하이브리드 오디언스</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>kk_3184721081</t>
+          <t>kk_4615977966</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>01085470105</t>
+          <t>01029473782</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>229171</t>
+          <t>290690</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0209_NEWYEAR</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>swsun9</t>
+          <t>kk_4516410827</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>01097889718</t>
+          <t>01048475313</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>295157</t>
+          <t>285997</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -979,24 +979,24 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>da</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>sky2446</t>
+          <t>kk_5036115734</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>01086189169</t>
+          <t>01046709214</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>310077</t>
+          <t>311217</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1006,24 +1006,24 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>sooenter2021</t>
+          <t>kk_5048808976</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>01051830725</t>
+          <t>01026908279</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>310304</t>
+          <t>311623</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1033,51 +1033,51 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>kk_3775635739</t>
+          <t>kk_4387186836</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>01047873237</t>
+          <t>01085670209</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>255851</t>
+          <t>280506</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>[PF]A+SC_상시(1865MF,논타겟)</t>
+          <t>0716_SEASON_OFF_2ND</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>kk_3147981567</t>
+          <t>romanohong</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>01072033421</t>
+          <t>01089301124</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>223217</t>
+          <t>32607</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1087,78 +1087,78 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0702_REVERSEDOWN</t>
+          <t>0520</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>kk_4209546622</t>
+          <t>kk_5050299156</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>01079193288</t>
+          <t>01026976598</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>272272</t>
+          <t>311666</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>kk_4315111161</t>
+          <t>naroo27</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>01080806591</t>
+          <t>01075300052</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>277461</t>
+          <t>102129</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0425_FAMILYSALE</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>kk_4647481524</t>
+          <t>kk_3179837389</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>01030569095</t>
+          <t>01089490421</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>292864</t>
+          <t>225507</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1168,132 +1168,132 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>0803_SUMMER_LAST_CHANCE</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>hajd1011</t>
+          <t>kk_4582648301</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>01054401373</t>
+          <t>01040451815</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>283249</t>
+          <t>288564</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>kk_5008721553</t>
+          <t>aceykh</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>01089905677</t>
+          <t>01041402352</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>310248</t>
+          <t>140002</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>EDM_TOP</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>kk_4615977966</t>
+          <t>kk_4481940140</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>01029473782</t>
+          <t>01065676272</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>290690</t>
+          <t>284338</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>[PF_SA] 컬럼비아 상시</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>kk_4516410827</t>
+          <t>aaeolus</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>01048475313</t>
+          <t>01082605032</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>285997</t>
+          <t>282510</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>etc</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>kk_5036115734</t>
+          <t>kk_3772986666</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>01046709214</t>
+          <t>01085470459</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>311217</t>
+          <t>255687</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1303,105 +1303,105 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>kk_2751892064_2</t>
+          <t>wnsvy2957</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>01044569101</t>
+          <t>01052632952</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>282142</t>
+          <t>283008</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자30일)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>kk_5048808976</t>
+          <t>kk_3182977787</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>01026908279</t>
+          <t>01085398119</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>311623</t>
+          <t>228089</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>kk_4940334145</t>
+          <t>kk_2845811024_3</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>01025490108</t>
+          <t>01083771174</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>307549</t>
+          <t>307634</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>kk_4387186836</t>
+          <t>kk_3047832258</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>01085670209</t>
+          <t>01053403023</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>280506</t>
+          <t>220442</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1411,83 +1411,83 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0716_SEASON_OFF_2ND</t>
+          <t>EDM_0329</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>romanohong</t>
+          <t>kk_5053571972</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>01089301124</t>
+          <t>01062303845</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>32607</t>
+          <t>311761</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0520</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>uofnywam</t>
+          <t>kk_5041074251</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>01025062538</t>
+          <t>01058983349</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>204156</t>
+          <t>311361</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>120253016536170385</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>chokiwbang</t>
+          <t>kk_3099382486</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>01052258818</t>
+          <t>01093078148</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>140204</t>
+          <t>221525</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1499,152 +1499,152 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>kk_4468049816</t>
+          <t>kk_5054179034</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>01079335600</t>
+          <t>01066850120</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>283582</t>
+          <t>311781</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0226_BTS</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>kk_5050299156</t>
+          <t>kk_4997974077</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>01026976598</t>
+          <t>01040095693</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>311666</t>
+          <t>309775</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>naroo27</t>
+          <t>yk8809</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>01075300052</t>
+          <t>01023568809</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>102129</t>
+          <t>199548</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0425_FAMILYSALE</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>kk_3179837389</t>
+          <t>dyckim</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>01089490421</t>
+          <t>01044401262</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>225507</t>
+          <t>310573</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0803_SUMMER_LAST_CHANCE</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>kk_4582648301</t>
+          <t>khs0905</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>01040451815</t>
+          <t>01076640154</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>288564</t>
+          <t>137732</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>aceykh</t>
+          <t>nada1989</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>01041402352</t>
+          <t>01089413334</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>140002</t>
+          <t>203214</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1654,105 +1654,105 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>EDM_TOP</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>kk_3849010182</t>
+          <t>kk_3111973500</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>01071058942</t>
+          <t>01064187132</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>264944</t>
+          <t>267677</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>kk_4481940140</t>
+          <t>redsuede</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>01065676272</t>
+          <t>01032879838</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>284338</t>
+          <t>273348</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>[PF_SA] 컬럼비아 상시</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>aaeolus</t>
+          <t>kk_5052884183</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>01082605032</t>
+          <t>01030388284</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>282510</t>
+          <t>311732</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>naversa_pc</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>kk_3769382715</t>
+          <t>kk_5053135733</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>01098220944</t>
+          <t>01062083028</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>255392</t>
+          <t>311742</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1762,159 +1762,159 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>kk_3772986666</t>
+          <t>kk_5053813602</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>01085470459</t>
+          <t>01094931734</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>255687</t>
+          <t>311771</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>etc</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>herowill</t>
+          <t>kk_5052996890</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>01088996520</t>
+          <t>01028467527</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>85660</t>
+          <t>311736</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>etc</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>wnsvy2957</t>
+          <t>kk_4830179048</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>01052632952</t>
+          <t>01059171953</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>283008</t>
+          <t>303507</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naversa_mo</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>kk_3182977787</t>
+          <t>hhgg6482</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>01085398119</t>
+          <t>01052195642</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>228089</t>
+          <t>290916</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>kk_2845811024_3</t>
+          <t>kk_5052989693</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>01083771174</t>
+          <t>01095421888</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>307634</t>
+          <t>311735</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>etc</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>kk_3047832258</t>
+          <t>lees0925</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>01053403023</t>
+          <t>01089944951</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>220442</t>
+          <t>284991</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1924,51 +1924,51 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>EDM_0329</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>kk_4319247532</t>
+          <t>kk_5053146625</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>01088594122</t>
+          <t>01092265566</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>277718</t>
+          <t>311743</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>etc</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>kk_5053571972</t>
+          <t>kk_5040443935</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>01062303845</t>
+          <t>01086507863</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>311761</t>
+          <t>311339</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1978,24 +1978,24 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>[PF]전환_상시(2565MF,비구매자30일)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>kk_5041074251</t>
+          <t>molgue</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>01058983349</t>
+          <t>01096385787</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>311361</t>
+          <t>189580</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2005,186 +2005,186 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>120253016536170385</t>
+          <t>방문_하이브리드 오디언스</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>tmdwosnsk</t>
+          <t>kk_5053573200</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>01040847350</t>
+          <t>01050217981</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>239452</t>
+          <t>311762</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>kk_3099382486</t>
+          <t>kk_3392066640</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>01093078148</t>
+          <t>01065021283</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>221525</t>
+          <t>240983</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>kk_5054179034</t>
+          <t>kk_3140884947</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>01066850120</t>
+          <t>01081538888</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>311781</t>
+          <t>222841</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>0818_BRANDTALK_JONAS</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>kk_4997974077</t>
+          <t>kk_4445795434</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>01040095693</t>
+          <t>01027315428</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>309775</t>
+          <t>282265</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>0803_Clearance</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>yk8809</t>
+          <t>icoram</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>01023568809</t>
+          <t>01091898092</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>199548</t>
+          <t>311807</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>dyckim</t>
+          <t>kk_3222864535</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>01044401262</t>
+          <t>01087438761</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>310573</t>
+          <t>232810</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>kk_5051879020</t>
+          <t>kk_5052196631</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>01071731874</t>
+          <t>01035951351</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>311712</t>
+          <t>311723</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2194,24 +2194,24 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>itsuky3785</t>
+          <t>kk_4915210068</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>01033352103</t>
+          <t>01054111693</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>288167</t>
+          <t>306647</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2221,186 +2221,186 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>khs0905</t>
+          <t>kk_4286220576</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>01076640154</t>
+          <t>01053587782</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>137732</t>
+          <t>275624</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>LMS_ECOM_200416_seasonoff</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>nada1989</t>
+          <t>kk_2919185721</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>01089413334</t>
+          <t>01034872320</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>203214</t>
+          <t>215776</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>etc</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>kk_3111973500</t>
+          <t>kk_4213116180</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>01064187132</t>
+          <t>01094956022</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>267677</t>
+          <t>272450</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKO_CH_MESSAGE_0817_SUMMERCLEARANCE</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>redsuede</t>
+          <t>ghffhs</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>01032879838</t>
+          <t>01086461880</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>273348</t>
+          <t>172816</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>kk_5052884183</t>
+          <t>kk_3211764926</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>01030388284</t>
+          <t>01065592320</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>311732</t>
+          <t>231794</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>naversa_pc</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>kk_5053135733</t>
+          <t>jsy90</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>01062083028</t>
+          <t>01055153689</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>311742</t>
+          <t>304378</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0410pants2</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>kk_4671019003</t>
+          <t>kk_3923084698</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>01064700873</t>
+          <t>01093992638</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>294341</t>
+          <t>268693</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2410,159 +2410,159 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>kk_5049890573</t>
+          <t>kk_4902163917</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>01094328346</t>
+          <t>01091388108</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>311657</t>
+          <t>306260</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>kk_5051471907</t>
+          <t>kk_5054290902</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>01092552888</t>
+          <t>01089708874</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>311705</t>
+          <t>311785</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>kk_5053813602</t>
+          <t>kkk570908</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>01094931734</t>
+          <t>01037997125</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>311771</t>
+          <t>268558</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>da</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>kk_5052996890</t>
+          <t>kk_3415923718</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>01028467527</t>
+          <t>01087476815</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>311736</t>
+          <t>241616</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>da</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>kk_4830179048</t>
+          <t>younge789</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>01059171953</t>
+          <t>01085185168</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>303507</t>
+          <t>169078</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>hhgg6482</t>
+          <t>kk_5054464771</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>01052195642</t>
+          <t>01087583944</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>290916</t>
+          <t>311791</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2572,78 +2572,78 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>sclpion</t>
+          <t>kk_3157182568</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>01088740653</t>
+          <t>01057620105</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>141669</t>
+          <t>223820</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>gogo4135</t>
+          <t>happyglory81</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>01088831877</t>
+          <t>01064760332</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>170683</t>
+          <t>135652</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>fcozy</t>
+          <t>kk_5052645690</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>01083998861</t>
+          <t>01094486334</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>114021</t>
+          <t>311729</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2653,132 +2653,132 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>kk_5052989693</t>
+          <t>kk_5054057588</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>01095421888</t>
+          <t>01047332261</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>311735</t>
+          <t>311778</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>lees0925</t>
+          <t>kk_3303914582</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>01089944951</t>
+          <t>01028715525</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>284991</t>
+          <t>237924</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>kk_5053146625</t>
+          <t>kk_5050311909</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>01092265566</t>
+          <t>01039067015</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>311743</t>
+          <t>311667</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>KAKAO_CH_MENU_0728_AMBASSADOR</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>kk_5040443935</t>
+          <t>daekwangsu</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>01086507863</t>
+          <t>01055970579</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>311339</t>
+          <t>96203</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자30일)</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>kk_5050610678</t>
+          <t>kk_3622891451</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>01093820086</t>
+          <t>01053726280</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>311678</t>
+          <t>247735</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2788,105 +2788,105 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>russia55</t>
+          <t>kk_3842461525</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>01022813614</t>
+          <t>01077300704</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>170004</t>
+          <t>264453</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>0520</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>molgue</t>
+          <t>merhen</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>01096385787</t>
+          <t>01025129134</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>189580</t>
+          <t>89491</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>방문_하이브리드 오디언스</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>kk_4234730563</t>
+          <t>kk_3728610953</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>01072748373</t>
+          <t>01092914950</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>273531</t>
+          <t>252762</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>piung8</t>
+          <t>kk_5053760478</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>01024302128</t>
+          <t>01025944738</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>241561</t>
+          <t>311768</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2896,24 +2896,24 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>kk_5053573200</t>
+          <t>ic8871</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>01050217981</t>
+          <t>01063456741</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>311762</t>
+          <t>117110</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -2923,429 +2923,429 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>kk_2794341634</t>
+          <t>sm297</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>01062258622</t>
+          <t>01089954070</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>210525</t>
+          <t>172466</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>etc</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>humi312</t>
+          <t>sunam12</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>01032018321</t>
+          <t>01081404180</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>109372</t>
+          <t>148548</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>방문_하이브리드 오디언스</t>
+          <t>KAKAO_CH_MESSAGE_260702_SEASONOFF2ND</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>kk_3392066640</t>
+          <t>soleado</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>01065021283</t>
+          <t>01067078981</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>240983</t>
+          <t>289679</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>kk_3140884947</t>
+          <t>wjddmsp4</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>01081538888</t>
+          <t>01027170361</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>222841</t>
+          <t>103841</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>0818_BRANDTALK_JONAS</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>kk_4445795434</t>
+          <t>kk_4442668340</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>01027315428</t>
+          <t>01089979956</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>282265</t>
+          <t>282163</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>0803_Clearance</t>
+          <t>etc</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>mupasa1010</t>
+          <t>kk_4679174258</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>01098195600</t>
+          <t>01054503197</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>197579</t>
+          <t>294810</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>kk_4967367828</t>
+          <t>kk_5053440830</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>01090955298</t>
+          <t>01075725067</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>308392</t>
+          <t>311758</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>방문_하이브리드 오디언스</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>icoram</t>
+          <t>mgoon1005</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>01091898092</t>
+          <t>01054720108</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>311807</t>
+          <t>266467</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>kk_3222864535</t>
+          <t>kk_3733604305</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>01087438761</t>
+          <t>01046180063</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>232810</t>
+          <t>253138</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_MESSAGE_0730_OMNISHADE</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>della96</t>
+          <t>dbeodus12</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>01071782565</t>
+          <t>01094952956</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>119198</t>
+          <t>177779</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>방문_하이브리드 오디언스</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>kk_5052196631</t>
+          <t>kk_5025530724</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>01035951351</t>
+          <t>01055050266</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>311723</t>
+          <t>310814</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>kk_4915210068</t>
+          <t>bluesung226</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>01054111693</t>
+          <t>01024421910</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>306647</t>
+          <t>205476</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>kk_4286220576</t>
+          <t>kk_5054226033</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>01053587782</t>
+          <t>01084058475</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>275624</t>
+          <t>311784</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>LMS_ECOM_200416_seasonoff</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>kk_2919185721</t>
+          <t>kk_3372478035</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>01034872320</t>
+          <t>01073318137</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>215776</t>
+          <t>240206</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>kk_4213116180</t>
+          <t>seomina0907</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>01094956022</t>
+          <t>01094631272</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>272450</t>
+          <t>166015</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>KAKO_CH_MESSAGE_0817_SUMMERCLEARANCE</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ghffhs</t>
+          <t>kk_5053805303</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>01086461880</t>
+          <t>01035199923</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>172816</t>
+          <t>311769</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3362,17 +3362,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>hiyeom</t>
+          <t>bambae74</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>01092193123</t>
+          <t>01037840714</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>73820</t>
+          <t>68767</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3389,206 +3389,206 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>kk_3211764926</t>
+          <t>kk_4977819786</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>01065592320</t>
+          <t>01063257991</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>231794</t>
+          <t>308849</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>jsy90</t>
+          <t>kk_5050508246</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>01055153689</t>
+          <t>01099167304</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>304378</t>
+          <t>311676</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410pants2</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>kk_3923084698</t>
+          <t>dhk1827</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>01093992638</t>
+          <t>01027971827</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>268693</t>
+          <t>286842</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>kk_4902163917</t>
+          <t>kk_5029461637</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>01091388108</t>
+          <t>01037759598</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>306260</t>
+          <t>310962</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>kk_5054290902</t>
+          <t>kk_3163403095</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>01089708874</t>
+          <t>01094442663</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>311785</t>
+          <t>224415</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKO_CH_MESSAGE_0817_SUMMERCLEARANCE</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>kkk570908</t>
+          <t>kk_5054920254</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>01037997125</t>
+          <t>01093769998</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>268558</t>
+          <t>311799</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>kk_3415923718</t>
+          <t>kk_5055001343</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>01087476815</t>
+          <t>01047875895</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>241616</t>
+          <t>311801</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>younge789</t>
+          <t>kk_5052988564</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>01085185168</t>
+          <t>01047680429</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>169078</t>
+          <t>311734</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -3605,98 +3605,98 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>kk_5054464771</t>
+          <t>djae63</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>01087583944</t>
+          <t>01027633204</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>311791</t>
+          <t>245415</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>kk_3157182568</t>
+          <t>kk_3864552155</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>01057620105</t>
+          <t>01035193074</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>223820</t>
+          <t>265863</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>happyglory81</t>
+          <t>kk_5052479419</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>01064760332</t>
+          <t>01047117155</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>135652</t>
+          <t>311726</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>kk_5052645690</t>
+          <t>kk_2867961634</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>01094486334</t>
+          <t>01033939933</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>311729</t>
+          <t>213870</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -3713,17 +3713,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>kk_5054057588</t>
+          <t>kk_5053401059</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>01047332261</t>
+          <t>01021051426</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>311778</t>
+          <t>311756</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -3740,17 +3740,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>kk_4288755561</t>
+          <t>kkjjg123</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>01042420896</t>
+          <t>01036960451</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>275791</t>
+          <t>110344</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -3760,267 +3760,267 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>KAKO_CH_MESSAGE_0817_TRAILRUN</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>kk_3303914582</t>
+          <t>seep</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>01028715525</t>
+          <t>01051600565</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>237924</t>
+          <t>112406</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>kk_5050311909</t>
+          <t>kk_5053312014</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>01039067015</t>
+          <t>01076680710</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>311667</t>
+          <t>311750</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0728_AMBASSADOR</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>daekwangsu</t>
+          <t>son2245</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>01055970579</t>
+          <t>01039192245</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>96203</t>
+          <t>164240</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>kk_3622891451</t>
+          <t>kk_5055289049</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>01053726280</t>
+          <t>01029088281</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>247735</t>
+          <t>311808</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>kk_3842461525</t>
+          <t>kk_3626416291</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>01077300704</t>
+          <t>01049003915</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>264453</t>
+          <t>247860</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>0520</t>
+          <t>etc</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>merhen</t>
+          <t>minjin6789</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>01025129134</t>
+          <t>01024062050</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>89491</t>
+          <t>157791</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>kk_3728610953</t>
+          <t>kk_5054844830</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>01092914950</t>
+          <t>01025386330</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>252762</t>
+          <t>311796</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>gusrb5315</t>
+          <t>kk_3156778149</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>01033445315</t>
+          <t>01084700197</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>240662</t>
+          <t>223775</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>kk_5053760478</t>
+          <t>kk_5053032122</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>01025944738</t>
+          <t>01053783882</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>311768</t>
+          <t>311739</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ic8871</t>
+          <t>kk_5053223845</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>01063456741</t>
+          <t>01096775572</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>117110</t>
+          <t>311747</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -4030,51 +4030,51 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>da</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>sm297</t>
+          <t>woogi1223</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>01089954070</t>
+          <t>01044556757</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>172466</t>
+          <t>234672</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>sunam12</t>
+          <t>kk_2756203834</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>01081404180</t>
+          <t>01072683457</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>148548</t>
+          <t>208171</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -4084,159 +4084,159 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_260702_SEASONOFF2ND</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>soleado</t>
+          <t>kk_3628470198</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>01067078981</t>
+          <t>01063886569</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>289679</t>
+          <t>247993</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>kk_3035383266</t>
+          <t>kk_5054386338</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>01036728869</t>
+          <t>01028827342</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>219867</t>
+          <t>311788</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>wjddmsp4</t>
+          <t>kk_3800038767</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>01027170361</t>
+          <t>01045487979</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>103841</t>
+          <t>258758</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>kk_4442668340</t>
+          <t>kk_5055221035</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>01089979956</t>
+          <t>01090429853</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>282163</t>
+          <t>311804</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>kk_4679174258</t>
+          <t>kk_5054440771</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>01054503197</t>
+          <t>01034218601</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>294810</t>
+          <t>311790</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>kk_5053440830</t>
+          <t>kk_5053502414</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>01075725067</t>
+          <t>01062768083</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>311758</t>
+          <t>311760</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -4246,51 +4246,51 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>방문_하이브리드 오디언스</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>kk_5026095899</t>
+          <t>jjun0297</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>01086935544</t>
+          <t>01097027205</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>310852</t>
+          <t>156884</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>mgoon1005</t>
+          <t>hans7171</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>01054720108</t>
+          <t>01036045283</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>266467</t>
+          <t>223933</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -4300,1735 +4300,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>kk_3666720704</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>01033458251</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>249880</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>KAKAO_CH_MESSAGE_260702_WATERPROOFITEM</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>kk_3733604305</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>01046180063</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>253138</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>KAKAO_CH_MESSAGE_0730_OMNISHADE</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>dbeodus12</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>01094952956</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>177779</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>kk_5025530724</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>01055050266</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>310814</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>Official SNS</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>(referral)</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>kk_4442439433</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>01075664837</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>282157</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>0520</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>bluesung226</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>01024421910</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>205476</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>Email_mkt</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>kk_3168093587</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>01087964559</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>224737</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>naver_brandsearch_mobile</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>kk_5054226033</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>01084058475</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>311784</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>kk_5052086920</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>01087726668</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>311718</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>etc</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>june715</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>01071157671</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>172897</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>KAKAO_CH_MENU_260603_SEASONOFF</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>kk_3372478035</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>01073318137</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>240206</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>seomina0907</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>01094631272</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>166015</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>kk_5053805303</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>01035199923</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>311769</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>bambae74</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>01037840714</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>68767</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>da</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>jscho01</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>01053208316</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>139260</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>kk_4977819786</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>01063257991</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>308849</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>naver_brandsearch_mobile</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>kk_5050508246</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>01099167304</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>311676</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>미분류</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>dhk1827</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>01027971827</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>286842</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>kk_2846130578</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>01064075652</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>213236</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>120253016536170385</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>kk_5029461637</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>01037759598</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>310962</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>yan01062</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>01076707692</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>203357</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>sa</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>kk_3163403095</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>01094442663</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>224415</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>KAKO_CH_MESSAGE_0817_SUMMERCLEARANCE</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>kk_5054920254</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>01093769998</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>311799</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>kk_5055001343</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>01047875895</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>311801</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>kk_3685066575</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>01021696118</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>250622</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>naver_brandsearch_mobile</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>wasserland</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>01051765220</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>177860</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>Email_mkt</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>kk_3180692048</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>01046133289</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>226239</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>미분류</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>kk_5052988564</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>01047680429</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>311734</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>djae63</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>01027633204</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>245415</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>sa</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>kk_3864552155</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>01035193074</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>265863</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>kk_5052479419</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>01047117155</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>311726</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>naver_brandsearch_mobile</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>kk_2867961634</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>01033939933</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>213870</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>naver_brandsearch_mobile</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>kk_5053401059</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>01021051426</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>311756</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>kkjjg123</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>01036960451</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>110344</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>KAKAO_alimtalk</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>seep</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>01051600565</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>112406</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>naver_brandsearch_mobile</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>kk_5053312014</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>01076680710</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>311750</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>son2245</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>01039192245</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>164240</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>미분류</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>kk_5055289049</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>01029088281</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>311808</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>kk_5050974529</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>01023991588</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>311692</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>KAKO_CH_MESSAGE_0817_SUMMERCLEARANCE</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>kk_3476177906</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>01079305414</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>244235</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>minjin6789</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>01024062050</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>157791</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>kk_5054844830</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>01025386330</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>311796</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>kk_3626416291</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>01049003915</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>247860</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>etc</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>kk_3156778149</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>01084700197</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>223775</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>KAKAO_alimtalk</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>kk_5053032122</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>01053783882</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>311739</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>kk_5053223845</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>01096775572</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>311747</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>da</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>kk_5051084066</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>01032038750</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>311696</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>Organic Traffic</t>
-        </is>
-      </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>(referral)</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>attack0418</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>01094139645</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>110090</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>bizboard</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>priscus</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>01083762352</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>105660</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>Email_mkt</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>woogi1223</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>01044556757</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>234672</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>rlaxotn1000</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>01091325436</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>155814</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>kk_2756203834</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>01072683457</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>208171</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>kk_3628470198</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>01063886569</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>247993</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>kk_5055221035</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>01090429853</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>311804</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>kk_5054386338</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>01028827342</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>311788</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>kk_3800038767</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>01045487979</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>258758</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>kk_5054440771</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>01034218601</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>311790</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>kk_5053502414</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>01062768083</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>311760</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>naver_brandsearch_pc</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>real3on3</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>01052726330</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>136007</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>jjun0297</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>01097027205</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>156884</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>hans7171</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>01036045283</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>223933</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E205" t="inlineStr">
-        <is>
           <t>방문_하이브리드 오디언스</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>kk_5051867525</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>01075564274</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>311711</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>nls6320</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>01036986321</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>28085</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>방문_하이브리드 오디언스</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>biueskymin</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>01027873593</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>159720</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>Direct</t>
         </is>
       </c>
     </row>

--- a/reports/member_funnel/downloads/member_funnel_1m_non_buyer.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1m_non_buyer.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E144"/>
+  <dimension ref="A1:E84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,71 +500,71 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>kk_4993751323</t>
+          <t>kk_4403816883</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>01053138487</t>
+          <t>01097910906</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>309590</t>
+          <t>280909</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>방문_하이브리드 오디언스</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>kk_4403816883</t>
+          <t>kk_3840423259</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>01097910906</t>
+          <t>01050355480</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>280909</t>
+          <t>264298</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>kk_3840423259</t>
+          <t>kk_5053218420</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>01050355480</t>
+          <t>01053426954</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>264298</t>
+          <t>311746</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -574,24 +574,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>kk_5053218420</t>
+          <t>kk_5034001705</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>01053426954</t>
+          <t>01090601731</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>311746</t>
+          <t>311133</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>gbj20022002</t>
+          <t>kk_5046820175</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>01053509041</t>
+          <t>01062781955</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>53032</t>
+          <t>311563</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -628,24 +628,24 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>방문_하이브리드 오디언스</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>kk_3433423317</t>
+          <t>honor181</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>01075326556</t>
+          <t>01046301211</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>242341</t>
+          <t>192770</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -662,44 +662,44 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>hjb007</t>
+          <t>jpm111</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>01096664026</t>
+          <t>01029304010</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>144397</t>
+          <t>249216</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>poweryys</t>
+          <t>kk_4209546622</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>01089678835</t>
+          <t>01079193288</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>214318</t>
+          <t>272272</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -709,51 +709,51 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kk_5034001705</t>
+          <t>kk_4315111161</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>01090601731</t>
+          <t>01080806591</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>311133</t>
+          <t>277461</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kk_5046820175</t>
+          <t>kk_5008721553</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>01062781955</t>
+          <t>01089905677</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>311563</t>
+          <t>310248</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -763,132 +763,132 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>방문_하이브리드 오디언스</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>honor181</t>
+          <t>kk_4615977966</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>01046301211</t>
+          <t>01029473782</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>192770</t>
+          <t>290690</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>jpm111</t>
+          <t>kk_4516410827</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>01029304010</t>
+          <t>01048475313</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>249216</t>
+          <t>285997</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>da</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>kk_3147981567</t>
+          <t>kk_5036115734</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>01072033421</t>
+          <t>01046709214</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>223217</t>
+          <t>311217</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0702_REVERSEDOWN</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>kk_4209546622</t>
+          <t>kk_5048808976</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>01079193288</t>
+          <t>01026908279</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>272272</t>
+          <t>311623</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>kk_4315111161</t>
+          <t>kk_4387186836</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>01080806591</t>
+          <t>01085670209</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>277461</t>
+          <t>280506</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -898,132 +898,132 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>0716_SEASON_OFF_2ND</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>kk_5008721553</t>
+          <t>romanohong</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>01089905677</t>
+          <t>01089301124</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>310248</t>
+          <t>32607</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>0520</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>kk_4615977966</t>
+          <t>naroo27</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>01029473782</t>
+          <t>01075300052</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>290690</t>
+          <t>102129</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>LMS_ECOM_0425_FAMILYSALE</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>kk_4516410827</t>
+          <t>kk_3179837389</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>01048475313</t>
+          <t>01089490421</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>285997</t>
+          <t>225507</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>0803_SUMMER_LAST_CHANCE</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>kk_5036115734</t>
+          <t>kk_4582648301</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>01046709214</t>
+          <t>01040451815</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>311217</t>
+          <t>288564</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>kk_5048808976</t>
+          <t>kk_3772986666</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>01026908279</t>
+          <t>01085470459</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>311623</t>
+          <t>255687</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1033,24 +1033,24 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>kk_4387186836</t>
+          <t>wnsvy2957</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>01085670209</t>
+          <t>01052632952</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>280506</t>
+          <t>283008</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1060,51 +1060,51 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0716_SEASON_OFF_2ND</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>romanohong</t>
+          <t>kk_5041074251</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>01089301124</t>
+          <t>01058983349</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>32607</t>
+          <t>311361</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0520</t>
+          <t>120253016536170385</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>kk_5050299156</t>
+          <t>kk_3099382486</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>01026976598</t>
+          <t>01093078148</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>311666</t>
+          <t>221525</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1114,78 +1114,78 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>naroo27</t>
+          <t>kk_5054179034</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>01075300052</t>
+          <t>01066850120</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>102129</t>
+          <t>311781</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0425_FAMILYSALE</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>kk_3179837389</t>
+          <t>kk_4997974077</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>01089490421</t>
+          <t>01040095693</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>225507</t>
+          <t>309775</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0803_SUMMER_LAST_CHANCE</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>kk_4582648301</t>
+          <t>yk8809</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>01040451815</t>
+          <t>01023568809</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>288564</t>
+          <t>199548</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1195,105 +1195,105 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>aceykh</t>
+          <t>dyckim</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>01041402352</t>
+          <t>01044401262</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>140002</t>
+          <t>310573</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>EDM_TOP</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>kk_4481940140</t>
+          <t>khs0905</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>01065676272</t>
+          <t>01076640154</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>284338</t>
+          <t>137732</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>[PF_SA] 컬럼비아 상시</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>aaeolus</t>
+          <t>nada1989</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>01082605032</t>
+          <t>01089413334</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>282510</t>
+          <t>203214</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>kk_3772986666</t>
+          <t>kk_4830179048</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>01085470459</t>
+          <t>01059171953</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>255687</t>
+          <t>303507</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1303,51 +1303,51 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naversa_mo</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>wnsvy2957</t>
+          <t>kk_5052989693</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>01052632952</t>
+          <t>01095421888</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>283008</t>
+          <t>311735</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>etc</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>kk_3182977787</t>
+          <t>kk_3392066640</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>01085398119</t>
+          <t>01065021283</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>228089</t>
+          <t>240983</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1357,105 +1357,105 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>kk_2845811024_3</t>
+          <t>kk_3140884947</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>01083771174</t>
+          <t>01081538888</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>307634</t>
+          <t>222841</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>0818_BRANDTALK_JONAS</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>kk_3047832258</t>
+          <t>icoram</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>01053403023</t>
+          <t>01091898092</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>220442</t>
+          <t>311807</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>EDM_0329</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>kk_5053571972</t>
+          <t>kk_3222864535</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>01062303845</t>
+          <t>01087438761</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>311761</t>
+          <t>232810</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>kk_5041074251</t>
+          <t>kk_4915210068</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>01058983349</t>
+          <t>01054111693</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>311361</t>
+          <t>306647</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1465,51 +1465,51 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>120253016536170385</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>kk_3099382486</t>
+          <t>ghffhs</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>01093078148</t>
+          <t>01086461880</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>221525</t>
+          <t>172816</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>kk_5054179034</t>
+          <t>kk_3211764926</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>01066850120</t>
+          <t>01065592320</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>311781</t>
+          <t>231794</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1526,314 +1526,314 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>kk_4997974077</t>
+          <t>jsy90</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>01040095693</t>
+          <t>01055153689</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>309775</t>
+          <t>304378</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>LMS_ECOM_0410pants2</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>yk8809</t>
+          <t>kk_4902163917</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>01023568809</t>
+          <t>01091388108</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>199548</t>
+          <t>306260</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>dyckim</t>
+          <t>kk_5054290902</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>01044401262</t>
+          <t>01089708874</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>310573</t>
+          <t>311785</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>khs0905</t>
+          <t>kkk570908</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>01076640154</t>
+          <t>01037997125</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>137732</t>
+          <t>268558</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>da</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>nada1989</t>
+          <t>younge789</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>01089413334</t>
+          <t>01085185168</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>203214</t>
+          <t>169078</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>kk_3111973500</t>
+          <t>kk_5054464771</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>01064187132</t>
+          <t>01087583944</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>267677</t>
+          <t>311791</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>redsuede</t>
+          <t>kk_3157182568</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>01032879838</t>
+          <t>01057620105</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>273348</t>
+          <t>223820</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>kk_5052884183</t>
+          <t>happyglory81</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>01030388284</t>
+          <t>01064760332</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>311732</t>
+          <t>135652</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>naversa_pc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>kk_5053135733</t>
+          <t>kk_5054057588</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>01062083028</t>
+          <t>01047332261</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>311742</t>
+          <t>311778</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>kk_5053813602</t>
+          <t>kk_3303914582</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>01094931734</t>
+          <t>01028715525</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>311771</t>
+          <t>237924</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>kk_5052996890</t>
+          <t>daekwangsu</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>01028467527</t>
+          <t>01055970579</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>311736</t>
+          <t>96203</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>kk_4830179048</t>
+          <t>kk_3622891451</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>01059171953</t>
+          <t>01053726280</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>303507</t>
+          <t>247735</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1843,78 +1843,78 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>hhgg6482</t>
+          <t>kk_3728610953</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>01052195642</t>
+          <t>01092914950</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>290916</t>
+          <t>252762</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>kk_5052989693</t>
+          <t>ic8871</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>01095421888</t>
+          <t>01063456741</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>311735</t>
+          <t>117110</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>lees0925</t>
+          <t>sm297</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>01089944951</t>
+          <t>01089954070</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>284991</t>
+          <t>172466</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1924,51 +1924,51 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>etc</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>kk_5053146625</t>
+          <t>kk_4679174258</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>01092265566</t>
+          <t>01054503197</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>311743</t>
+          <t>294810</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>kk_5040443935</t>
+          <t>mgoon1005</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>01086507863</t>
+          <t>01054720108</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>311339</t>
+          <t>266467</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1978,78 +1978,78 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자30일)</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>molgue</t>
+          <t>dbeodus12</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>01096385787</t>
+          <t>01094952956</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>189580</t>
+          <t>177779</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>방문_하이브리드 오디언스</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>kk_5053573200</t>
+          <t>kk_5025530724</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>01050217981</t>
+          <t>01055050266</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>311762</t>
+          <t>310814</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>kk_3392066640</t>
+          <t>bluesung226</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>01065021283</t>
+          <t>01024421910</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>240983</t>
+          <t>205476</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2059,78 +2059,78 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>kk_3140884947</t>
+          <t>kk_5054226033</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>01081538888</t>
+          <t>01084058475</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>222841</t>
+          <t>311784</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0818_BRANDTALK_JONAS</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>kk_4445795434</t>
+          <t>kk_3372478035</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>01027315428</t>
+          <t>01073318137</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>282265</t>
+          <t>240206</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0803_Clearance</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>icoram</t>
+          <t>seomina0907</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>01091898092</t>
+          <t>01094631272</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>311807</t>
+          <t>166015</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2147,98 +2147,98 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>kk_3222864535</t>
+          <t>kk_5050508246</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>01087438761</t>
+          <t>01099167304</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>232810</t>
+          <t>311676</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>kk_5052196631</t>
+          <t>dhk1827</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>01035951351</t>
+          <t>01027971827</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>311723</t>
+          <t>286842</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>kk_4915210068</t>
+          <t>kk_5029461637</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>01054111693</t>
+          <t>01037759598</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>306647</t>
+          <t>310962</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>kk_4286220576</t>
+          <t>kk_3163403095</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>01053587782</t>
+          <t>01094442663</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>275624</t>
+          <t>224415</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2248,132 +2248,132 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>LMS_ECOM_200416_seasonoff</t>
+          <t>KAKO_CH_MESSAGE_0817_SUMMERCLEARANCE</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>kk_2919185721</t>
+          <t>kk_5054920254</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>01034872320</t>
+          <t>01093769998</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>215776</t>
+          <t>311799</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>kk_4213116180</t>
+          <t>kk_5055001343</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>01094956022</t>
+          <t>01047875895</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>272450</t>
+          <t>311801</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>KAKO_CH_MESSAGE_0817_SUMMERCLEARANCE</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ghffhs</t>
+          <t>djae63</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>01086461880</t>
+          <t>01027633204</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>172816</t>
+          <t>245415</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>kk_3211764926</t>
+          <t>kk_3864552155</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>01065592320</t>
+          <t>01035193074</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>231794</t>
+          <t>265863</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>jsy90</t>
+          <t>kkjjg123</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>01055153689</t>
+          <t>01036960451</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>304378</t>
+          <t>110344</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2383,78 +2383,78 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410pants2</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>kk_3923084698</t>
+          <t>kk_5055289049</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>01093992638</t>
+          <t>01029088281</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>268693</t>
+          <t>311808</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>kk_4902163917</t>
+          <t>kk_5054844830</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>01091388108</t>
+          <t>01025386330</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>306260</t>
+          <t>311796</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>kk_5054290902</t>
+          <t>minjin6789</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>01089708874</t>
+          <t>01024062050</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>311785</t>
+          <t>157791</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2471,71 +2471,71 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>kkk570908</t>
+          <t>kk_3626416291</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>01037997125</t>
+          <t>01049003915</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>268558</t>
+          <t>247860</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>etc</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>kk_3415923718</t>
+          <t>kk_2756203834</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>01087476815</t>
+          <t>01072683457</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>241616</t>
+          <t>208171</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>younge789</t>
+          <t>kk_3628470198</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>01085185168</t>
+          <t>01063886569</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>169078</t>
+          <t>247993</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2552,44 +2552,44 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>kk_5054464771</t>
+          <t>kk_3800038767</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>01087583944</t>
+          <t>01045487979</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>311791</t>
+          <t>258758</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>kk_3157182568</t>
+          <t>kk_5054386338</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>01057620105</t>
+          <t>01028827342</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>223820</t>
+          <t>311788</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2606,71 +2606,71 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>happyglory81</t>
+          <t>kk_5054440771</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>01064760332</t>
+          <t>01034218601</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>135652</t>
+          <t>311790</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>kk_5052645690</t>
+          <t>kk_5055221035</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>01094486334</t>
+          <t>01090429853</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>311729</t>
+          <t>311804</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>kk_5054057588</t>
+          <t>jjun0297</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>01047332261</t>
+          <t>01097027205</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>311778</t>
+          <t>156884</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2681,1626 +2681,6 @@
       <c r="E84" t="inlineStr">
         <is>
           <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>kk_3303914582</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>01028715525</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>237924</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>kk_5050311909</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>01039067015</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>311667</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>KAKAO_CH_MENU_0728_AMBASSADOR</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>daekwangsu</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>01055970579</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>96203</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>kk_3622891451</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>01053726280</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>247735</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>LMS_ECOM_0214_newyear</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>kk_3842461525</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>01077300704</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>264453</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>0520</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>merhen</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>01025129134</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>89491</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>Organic Traffic</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>(organic)</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>kk_3728610953</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>01092914950</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>252762</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>KAKAO_CH_event</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>kk_5053760478</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>01025944738</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>311768</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>naver_brandsearch_pc</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>ic8871</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>01063456741</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>117110</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>sm297</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>01089954070</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>172466</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>etc</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>sunam12</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>01081404180</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>148548</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>KAKAO_CH_MESSAGE_260702_SEASONOFF2ND</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>soleado</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>01067078981</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>289679</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>미분류</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>wjddmsp4</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>01027170361</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>103841</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>naver_brandsearch_mobile</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>kk_4442668340</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>01089979956</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>282163</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>etc</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>kk_4679174258</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>01054503197</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>294810</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>KAKAO_CH_event</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>kk_5053440830</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>01075725067</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>311758</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>방문_하이브리드 오디언스</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>mgoon1005</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>01054720108</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>266467</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>kk_3733604305</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>01046180063</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>253138</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>KAKAO_CH_MESSAGE_0730_OMNISHADE</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>dbeodus12</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>01094952956</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>177779</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>kk_5025530724</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>01055050266</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>310814</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>Official SNS</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>(referral)</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>bluesung226</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>01024421910</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>205476</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>Email_mkt</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>kk_5054226033</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>01084058475</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>311784</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>kk_3372478035</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>01073318137</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>240206</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>seomina0907</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>01094631272</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>166015</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>kk_5053805303</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>01035199923</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>311769</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>bambae74</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>01037840714</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>68767</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>da</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>kk_4977819786</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>01063257991</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>308849</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>naver_brandsearch_mobile</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>kk_5050508246</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>01099167304</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>311676</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>미분류</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>dhk1827</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>01027971827</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>286842</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>kk_5029461637</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>01037759598</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>310962</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>kk_3163403095</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>01094442663</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>224415</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>KAKO_CH_MESSAGE_0817_SUMMERCLEARANCE</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>kk_5054920254</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>01093769998</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>311799</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>kk_5055001343</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>01047875895</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>311801</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>kk_5052988564</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>01047680429</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>311734</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>djae63</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>01027633204</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>245415</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>sa</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>kk_3864552155</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>01035193074</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>265863</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>kk_5052479419</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>01047117155</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>311726</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>naver_brandsearch_mobile</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>kk_2867961634</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>01033939933</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>213870</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>naver_brandsearch_mobile</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>kk_5053401059</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>01021051426</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>311756</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>kkjjg123</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>01036960451</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>110344</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>KAKAO_alimtalk</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>seep</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>01051600565</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>112406</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>naver_brandsearch_mobile</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>kk_5053312014</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>01076680710</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>311750</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>son2245</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>01039192245</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>164240</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>미분류</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>kk_5055289049</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>01029088281</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>311808</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>kk_3626416291</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>01049003915</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>247860</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>etc</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>minjin6789</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>01024062050</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>157791</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>kk_5054844830</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>01025386330</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>311796</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>kk_3156778149</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>01084700197</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>223775</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>KAKAO_alimtalk</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>kk_5053032122</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>01053783882</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>311739</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>kk_5053223845</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>01096775572</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>311747</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>da</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>woogi1223</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>01044556757</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>234672</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>kk_2756203834</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>01072683457</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>208171</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>kk_3628470198</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>01063886569</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>247993</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>kk_5054386338</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>01028827342</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>311788</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>kk_3800038767</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>01045487979</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>258758</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>kk_5055221035</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>01090429853</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>311804</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>kk_5054440771</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>01034218601</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>311790</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>kk_5053502414</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>01062768083</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>311760</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>naver_brandsearch_pc</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>jjun0297</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>01097027205</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>156884</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>hans7171</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>01036045283</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>223933</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>방문_하이브리드 오디언스</t>
         </is>
       </c>
     </row>
